--- a/InputData/elec/DRCo/Demand Response Costs.xlsx
+++ b/InputData/elec/DRCo/Demand Response Costs.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganM\Documents\eps-india\InputData\elec\DRCo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\elec\DRCo\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEF0D7B-AE7E-492D-9F00-BDB69042AD95}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="1170" windowWidth="22170" windowHeight="16110"/>
+    <workbookView xWindow="9150" yWindow="690" windowWidth="29520" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -22,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Demand Response_States'!$A$3:$AN$430</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Demand Response_States'!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,14 +38,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7375" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7365" uniqueCount="558">
   <si>
     <t>Utility Characteristics</t>
   </si>
@@ -1447,34 +1448,10 @@
     <t>(the "nonenergy industries" or "consumers" cash flow entities in the EPS).</t>
   </si>
   <si>
-    <t>nonenergy industries</t>
-  </si>
-  <si>
     <t>labor and consumers</t>
   </si>
   <si>
     <t>foreign entities</t>
-  </si>
-  <si>
-    <t>electricity suppliers</t>
-  </si>
-  <si>
-    <t>coal suppliers</t>
-  </si>
-  <si>
-    <t>natural gas and petroleum suppliers</t>
-  </si>
-  <si>
-    <t>biomass and biofuel suppliers</t>
-  </si>
-  <si>
-    <t>other energy suppliers</t>
-  </si>
-  <si>
-    <t>Cost ($/MW)</t>
-  </si>
-  <si>
-    <t>% of DR (dimensionless)</t>
   </si>
   <si>
     <t>BA Code</t>
@@ -1747,19 +1724,28 @@
     <t>We use the median cost per MW (rather than a  weighted average) because a few</t>
   </si>
   <si>
-    <t>India:US GDP per capita adjustment, see InputData/scaling-factors.xlsx</t>
+    <t>domestic industries</t>
+  </si>
+  <si>
+    <t>Unit: $/MW</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Unit: % of DR (dimensionless)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1914,13 +1900,19 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="40">
@@ -2445,7 +2437,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2623,6 +2615,7 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="17" xfId="11" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2945,24 +2938,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="49.265625" customWidth="1"/>
+    <col min="2" max="2" width="49.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>432</v>
       </c>
@@ -2970,139 +2963,129 @@
         <v>433</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="6">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="34">
         <v>0.9143</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A37">
-        <v>3.878298458735905E-2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -3110,40 +3093,40 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN432"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.265625" style="35" customWidth="1"/>
-    <col min="7" max="7" width="13.1328125" style="35" customWidth="1"/>
-    <col min="8" max="8" width="10.265625" style="35" customWidth="1"/>
-    <col min="9" max="9" width="14.86328125" style="35" customWidth="1"/>
-    <col min="10" max="12" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="32" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="37" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.1328125" style="1"/>
+    <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" style="35" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="35" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="35" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="35" customWidth="1"/>
+    <col min="10" max="12" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="37" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
@@ -3195,7 +3178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>4</v>
       </c>
@@ -3253,7 +3236,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:40" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:40" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
@@ -3267,7 +3250,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>428</v>
@@ -3375,7 +3358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="31">
         <v>2018</v>
       </c>
@@ -3389,7 +3372,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F4" s="4">
         <f>IFERROR(SUM(AD4,AI4)*10^3/T4,"")</f>
@@ -3501,7 +3484,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="31">
         <v>2018</v>
       </c>
@@ -3515,7 +3498,7 @@
         <v>25</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" ref="F5:I68" si="1">IFERROR(SUM(AD5,AI5)*10^3/T5,"")</f>
@@ -3627,7 +3610,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="31">
         <v>2018</v>
       </c>
@@ -3641,7 +3624,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="1"/>
@@ -3753,7 +3736,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="31">
         <v>2018</v>
       </c>
@@ -3767,7 +3750,7 @@
         <v>29</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" si="1"/>
@@ -3879,7 +3862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="31">
         <v>2018</v>
       </c>
@@ -3893,7 +3876,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
@@ -4005,7 +3988,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="31">
         <v>2018</v>
       </c>
@@ -4019,7 +4002,7 @@
         <v>31</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="1"/>
@@ -4131,7 +4114,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="31">
         <v>2018</v>
       </c>
@@ -4145,7 +4128,7 @@
         <v>34</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="F10" s="4">
         <f t="shared" si="1"/>
@@ -4257,7 +4240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="31">
         <v>2018</v>
       </c>
@@ -4271,7 +4254,7 @@
         <v>36</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F11" s="4">
         <f t="shared" si="1"/>
@@ -4383,7 +4366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="31">
         <v>2018</v>
       </c>
@@ -4397,7 +4380,7 @@
         <v>38</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="1"/>
@@ -4509,7 +4492,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="31">
         <v>2018</v>
       </c>
@@ -4517,13 +4500,13 @@
         <v>332</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="D13" s="33" t="s">
         <v>89</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
@@ -4635,7 +4618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="31">
         <v>2018</v>
       </c>
@@ -4649,7 +4632,7 @@
         <v>40</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F14" s="4" t="str">
         <f t="shared" si="1"/>
@@ -4761,7 +4744,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="31">
         <v>2018</v>
       </c>
@@ -4775,7 +4758,7 @@
         <v>42</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F15" s="4" t="str">
         <f t="shared" si="1"/>
@@ -4887,7 +4870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="31">
         <v>2018</v>
       </c>
@@ -4901,7 +4884,7 @@
         <v>25</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F16" s="4">
         <f t="shared" si="1"/>
@@ -5013,7 +4996,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="31">
         <v>2018</v>
       </c>
@@ -5027,7 +5010,7 @@
         <v>44</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F17" s="4">
         <f t="shared" si="1"/>
@@ -5139,7 +5122,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="31">
         <v>2018</v>
       </c>
@@ -5153,7 +5136,7 @@
         <v>46</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="1"/>
@@ -5265,7 +5248,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="31">
         <v>2018</v>
       </c>
@@ -5279,7 +5262,7 @@
         <v>48</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F19" s="4" t="str">
         <f t="shared" si="1"/>
@@ -5391,7 +5374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="31">
         <v>2018</v>
       </c>
@@ -5399,13 +5382,13 @@
         <v>814</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D20" s="33" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="1"/>
@@ -5517,7 +5500,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="31">
         <v>2018</v>
       </c>
@@ -5531,7 +5514,7 @@
         <v>36</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F21" s="4" t="str">
         <f t="shared" si="1"/>
@@ -5643,7 +5626,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="31">
         <v>2018</v>
       </c>
@@ -5657,7 +5640,7 @@
         <v>51</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="1"/>
@@ -5769,7 +5752,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="31">
         <v>2018</v>
       </c>
@@ -5783,7 +5766,7 @@
         <v>36</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="1"/>
@@ -5895,7 +5878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="31">
         <v>2018</v>
       </c>
@@ -5909,7 +5892,7 @@
         <v>54</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="1"/>
@@ -6021,7 +6004,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="31">
         <v>2018</v>
       </c>
@@ -6029,13 +6012,13 @@
         <v>1062</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D25" s="33" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F25" s="4" t="str">
         <f t="shared" si="1"/>
@@ -6147,7 +6130,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="31">
         <v>2018</v>
       </c>
@@ -6161,7 +6144,7 @@
         <v>23</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F26" s="4">
         <f t="shared" si="1"/>
@@ -6273,7 +6256,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="31">
         <v>2018</v>
       </c>
@@ -6287,7 +6270,7 @@
         <v>36</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F27" s="4">
         <f t="shared" si="1"/>
@@ -6399,7 +6382,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="31">
         <v>2018</v>
       </c>
@@ -6413,7 +6396,7 @@
         <v>29</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="1"/>
@@ -6525,7 +6508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="31">
         <v>2018</v>
       </c>
@@ -6539,7 +6522,7 @@
         <v>29</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="1"/>
@@ -6651,7 +6634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="31">
         <v>2018</v>
       </c>
@@ -6665,7 +6648,7 @@
         <v>36</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="1"/>
@@ -6777,7 +6760,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="31">
         <v>2018</v>
       </c>
@@ -6791,7 +6774,7 @@
         <v>36</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="1"/>
@@ -6903,7 +6886,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="31">
         <v>2018</v>
       </c>
@@ -7029,7 +7012,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="31">
         <v>2018</v>
       </c>
@@ -7043,7 +7026,7 @@
         <v>64</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="1"/>
@@ -7155,7 +7138,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="31">
         <v>2018</v>
       </c>
@@ -7169,7 +7152,7 @@
         <v>36</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="1"/>
@@ -7281,7 +7264,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="31">
         <v>2018</v>
       </c>
@@ -7289,13 +7272,13 @@
         <v>1889</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D35" s="33" t="s">
         <v>79</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="1"/>
@@ -7407,7 +7390,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="31">
         <v>2018</v>
       </c>
@@ -7421,7 +7404,7 @@
         <v>36</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="1"/>
@@ -7533,7 +7516,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="31">
         <v>2018</v>
       </c>
@@ -7547,7 +7530,7 @@
         <v>68</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F37" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7659,7 +7642,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" s="31">
         <v>2018</v>
       </c>
@@ -7673,7 +7656,7 @@
         <v>70</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F38" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7785,7 +7768,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="31">
         <v>2018</v>
       </c>
@@ -7799,7 +7782,7 @@
         <v>72</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="1"/>
@@ -7911,7 +7894,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" s="31">
         <v>2018</v>
       </c>
@@ -7925,7 +7908,7 @@
         <v>70</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F40" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8037,7 +8020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41" s="31">
         <v>2018</v>
       </c>
@@ -8051,7 +8034,7 @@
         <v>64</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F41" s="4">
         <f t="shared" si="1"/>
@@ -8163,7 +8146,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" s="31">
         <v>2018</v>
       </c>
@@ -8177,7 +8160,7 @@
         <v>48</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F42" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8289,7 +8272,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="31">
         <v>2018</v>
       </c>
@@ -8303,7 +8286,7 @@
         <v>77</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" si="1"/>
@@ -8415,7 +8398,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44" s="31">
         <v>2018</v>
       </c>
@@ -8429,7 +8412,7 @@
         <v>79</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" si="1"/>
@@ -8541,7 +8524,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45" s="31">
         <v>2018</v>
       </c>
@@ -8555,7 +8538,7 @@
         <v>62</v>
       </c>
       <c r="E45" s="33" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F45" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8667,7 +8650,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46" s="31">
         <v>2018</v>
       </c>
@@ -8681,7 +8664,7 @@
         <v>70</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F46" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8793,7 +8776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47" s="31">
         <v>2018</v>
       </c>
@@ -8807,7 +8790,7 @@
         <v>31</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F47" s="4">
         <f t="shared" si="1"/>
@@ -8919,7 +8902,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48" s="31">
         <v>2018</v>
       </c>
@@ -8933,7 +8916,7 @@
         <v>40</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F48" s="4">
         <f t="shared" si="1"/>
@@ -9045,7 +9028,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49" s="31">
         <v>2018</v>
       </c>
@@ -9059,7 +9042,7 @@
         <v>84</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F49" s="4">
         <f t="shared" si="1"/>
@@ -9171,7 +9154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50" s="31">
         <v>2018</v>
       </c>
@@ -9185,7 +9168,7 @@
         <v>54</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F50" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9297,7 +9280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51" s="31">
         <v>2018</v>
       </c>
@@ -9311,7 +9294,7 @@
         <v>77</v>
       </c>
       <c r="E51" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F51" s="4">
         <f t="shared" si="1"/>
@@ -9423,7 +9406,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52" s="31">
         <v>2018</v>
       </c>
@@ -9437,7 +9420,7 @@
         <v>29</v>
       </c>
       <c r="E52" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F52" s="4">
         <f t="shared" si="1"/>
@@ -9549,7 +9532,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53" s="31">
         <v>2018</v>
       </c>
@@ -9563,7 +9546,7 @@
         <v>89</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F53" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9675,7 +9658,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54" s="31">
         <v>2018</v>
       </c>
@@ -9689,7 +9672,7 @@
         <v>29</v>
       </c>
       <c r="E54" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F54" s="4">
         <f t="shared" si="1"/>
@@ -9801,7 +9784,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55" s="31">
         <v>2018</v>
       </c>
@@ -9815,7 +9798,7 @@
         <v>93</v>
       </c>
       <c r="E55" s="33" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F55" s="4">
         <f t="shared" si="1"/>
@@ -9927,7 +9910,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56" s="31">
         <v>2018</v>
       </c>
@@ -9941,7 +9924,7 @@
         <v>23</v>
       </c>
       <c r="E56" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F56" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10053,7 +10036,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A57" s="31">
         <v>2018</v>
       </c>
@@ -10067,7 +10050,7 @@
         <v>96</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F57" s="4">
         <f t="shared" si="1"/>
@@ -10179,7 +10162,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A58" s="31">
         <v>2018</v>
       </c>
@@ -10193,7 +10176,7 @@
         <v>29</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F58" s="4">
         <f t="shared" si="1"/>
@@ -10305,7 +10288,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A59" s="31">
         <v>2018</v>
       </c>
@@ -10319,7 +10302,7 @@
         <v>96</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F59" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10431,7 +10414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A60" s="31">
         <v>2018</v>
       </c>
@@ -10445,7 +10428,7 @@
         <v>93</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F60" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10557,7 +10540,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A61" s="31">
         <v>2018</v>
       </c>
@@ -10571,7 +10554,7 @@
         <v>36</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F61" s="4">
         <f t="shared" si="1"/>
@@ -10683,7 +10666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A62" s="31">
         <v>2018</v>
       </c>
@@ -10691,13 +10674,13 @@
         <v>3804</v>
       </c>
       <c r="C62" s="33" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="D62" s="33" t="s">
         <v>62</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F62" s="4">
         <f t="shared" si="1"/>
@@ -10809,7 +10792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A63" s="31">
         <v>2018</v>
       </c>
@@ -10935,7 +10918,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A64" s="31">
         <v>2018</v>
       </c>
@@ -10949,7 +10932,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F64" s="4">
         <f t="shared" si="1"/>
@@ -11061,7 +11044,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A65" s="31">
         <v>2018</v>
       </c>
@@ -11075,7 +11058,7 @@
         <v>104</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F65" s="4">
         <f t="shared" si="1"/>
@@ -11187,7 +11170,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A66" s="31">
         <v>2018</v>
       </c>
@@ -11201,7 +11184,7 @@
         <v>106</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F66" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11313,7 +11296,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A67" s="31">
         <v>2018</v>
       </c>
@@ -11327,7 +11310,7 @@
         <v>96</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F67" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11439,7 +11422,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A68" s="31">
         <v>2018</v>
       </c>
@@ -11453,7 +11436,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F68" s="4">
         <f t="shared" si="1"/>
@@ -11565,7 +11548,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A69" s="31">
         <v>2018</v>
       </c>
@@ -11579,7 +11562,7 @@
         <v>25</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F69" s="4">
         <f t="shared" ref="F69:I132" si="2">IFERROR(SUM(AD69,AI69)*10^3/T69,"")</f>
@@ -11691,7 +11674,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A70" s="31">
         <v>2018</v>
       </c>
@@ -11705,7 +11688,7 @@
         <v>111</v>
       </c>
       <c r="E70" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F70" s="4">
         <f t="shared" si="2"/>
@@ -11817,7 +11800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A71" s="31">
         <v>2018</v>
       </c>
@@ -11831,7 +11814,7 @@
         <v>113</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F71" s="4" t="str">
         <f t="shared" si="2"/>
@@ -11943,7 +11926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A72" s="31">
         <v>2018</v>
       </c>
@@ -11957,7 +11940,7 @@
         <v>84</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F72" s="4">
         <f t="shared" si="2"/>
@@ -12069,7 +12052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A73" s="31">
         <v>2018</v>
       </c>
@@ -12083,7 +12066,7 @@
         <v>116</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F73" s="4">
         <f t="shared" si="2"/>
@@ -12195,7 +12178,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A74" s="31">
         <v>2018</v>
       </c>
@@ -12203,13 +12186,13 @@
         <v>4295</v>
       </c>
       <c r="C74" s="33" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="D74" s="33" t="s">
         <v>54</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F74" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12321,7 +12304,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A75" s="31">
         <v>2018</v>
       </c>
@@ -12335,7 +12318,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F75" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12447,7 +12430,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A76" s="31">
         <v>2018</v>
       </c>
@@ -12461,7 +12444,7 @@
         <v>38</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F76" s="4">
         <f t="shared" si="2"/>
@@ -12573,7 +12556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A77" s="31">
         <v>2018</v>
       </c>
@@ -12587,7 +12570,7 @@
         <v>31</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F77" s="4">
         <f t="shared" si="2"/>
@@ -12699,7 +12682,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="78" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A78" s="31">
         <v>2018</v>
       </c>
@@ -12713,7 +12696,7 @@
         <v>40</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F78" s="4">
         <f t="shared" si="2"/>
@@ -12825,7 +12808,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A79" s="31">
         <v>2018</v>
       </c>
@@ -12839,7 +12822,7 @@
         <v>48</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F79" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12951,7 +12934,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A80" s="31">
         <v>2018</v>
       </c>
@@ -12965,7 +12948,7 @@
         <v>40</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F80" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13077,7 +13060,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A81" s="31">
         <v>2018</v>
       </c>
@@ -13091,7 +13074,7 @@
         <v>106</v>
       </c>
       <c r="E81" s="33" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="F81" s="4">
         <f t="shared" si="2"/>
@@ -13203,7 +13186,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A82" s="31">
         <v>2018</v>
       </c>
@@ -13217,7 +13200,7 @@
         <v>72</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F82" s="4">
         <f t="shared" si="2"/>
@@ -13329,7 +13312,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A83" s="31">
         <v>2018</v>
       </c>
@@ -13343,7 +13326,7 @@
         <v>25</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F83" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13455,7 +13438,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A84" s="31">
         <v>2018</v>
       </c>
@@ -13469,7 +13452,7 @@
         <v>70</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F84" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13581,7 +13564,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A85" s="31">
         <v>2018</v>
       </c>
@@ -13589,13 +13572,13 @@
         <v>4960</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D85" s="33" t="s">
         <v>68</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F85" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13707,7 +13690,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A86" s="31">
         <v>2018</v>
       </c>
@@ -13721,7 +13704,7 @@
         <v>128</v>
       </c>
       <c r="E86" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F86" s="4">
         <f t="shared" si="2"/>
@@ -13833,7 +13816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A87" s="31">
         <v>2018</v>
       </c>
@@ -13847,7 +13830,7 @@
         <v>23</v>
       </c>
       <c r="E87" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F87" s="4">
         <f t="shared" si="2"/>
@@ -13959,7 +13942,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A88" s="31">
         <v>2018</v>
       </c>
@@ -13973,7 +13956,7 @@
         <v>38</v>
       </c>
       <c r="E88" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F88" s="4">
         <f t="shared" si="2"/>
@@ -14085,7 +14068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A89" s="31">
         <v>2018</v>
       </c>
@@ -14099,7 +14082,7 @@
         <v>128</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F89" s="4">
         <f t="shared" si="2"/>
@@ -14211,7 +14194,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A90" s="31">
         <v>2018</v>
       </c>
@@ -14225,7 +14208,7 @@
         <v>54</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F90" s="4">
         <f t="shared" si="2"/>
@@ -14337,7 +14320,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A91" s="31">
         <v>2018</v>
       </c>
@@ -14351,7 +14334,7 @@
         <v>116</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F91" s="4">
         <f t="shared" si="2"/>
@@ -14463,7 +14446,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A92" s="31">
         <v>2018</v>
       </c>
@@ -14477,7 +14460,7 @@
         <v>36</v>
       </c>
       <c r="E92" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F92" s="4">
         <f t="shared" si="2"/>
@@ -14589,7 +14572,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A93" s="31">
         <v>2018</v>
       </c>
@@ -14603,7 +14586,7 @@
         <v>128</v>
       </c>
       <c r="E93" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F93" s="4" t="str">
         <f t="shared" si="2"/>
@@ -14715,7 +14698,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A94" s="31">
         <v>2018</v>
       </c>
@@ -14729,7 +14712,7 @@
         <v>96</v>
       </c>
       <c r="E94" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F94" s="4" t="str">
         <f t="shared" si="2"/>
@@ -14841,7 +14824,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A95" s="31">
         <v>2018</v>
       </c>
@@ -14855,7 +14838,7 @@
         <v>79</v>
       </c>
       <c r="E95" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F95" s="4" t="str">
         <f t="shared" si="2"/>
@@ -14967,7 +14950,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A96" s="31">
         <v>2018</v>
       </c>
@@ -14981,7 +14964,7 @@
         <v>62</v>
       </c>
       <c r="E96" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F96" s="4" t="str">
         <f t="shared" si="2"/>
@@ -15093,7 +15076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A97" s="31">
         <v>2018</v>
       </c>
@@ -15107,7 +15090,7 @@
         <v>29</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F97" s="4">
         <f t="shared" si="2"/>
@@ -15219,7 +15202,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A98" s="31">
         <v>2018</v>
       </c>
@@ -15233,7 +15216,7 @@
         <v>111</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F98" s="4">
         <f t="shared" si="2"/>
@@ -15345,7 +15328,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A99" s="31">
         <v>2018</v>
       </c>
@@ -15353,13 +15336,13 @@
         <v>5487</v>
       </c>
       <c r="C99" s="33" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="D99" s="33" t="s">
         <v>89</v>
       </c>
       <c r="E99" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F99" s="4" t="str">
         <f t="shared" si="2"/>
@@ -15471,7 +15454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A100" s="31">
         <v>2018</v>
       </c>
@@ -15485,7 +15468,7 @@
         <v>64</v>
       </c>
       <c r="E100" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F100" s="4">
         <f t="shared" si="2"/>
@@ -15597,7 +15580,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="101" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A101" s="31">
         <v>2018</v>
       </c>
@@ -15611,7 +15594,7 @@
         <v>36</v>
       </c>
       <c r="E101" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F101" s="4">
         <f t="shared" si="2"/>
@@ -15723,7 +15706,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="102" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A102" s="31">
         <v>2018</v>
       </c>
@@ -15737,7 +15720,7 @@
         <v>142</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F102" s="4" t="str">
         <f t="shared" si="2"/>
@@ -15849,7 +15832,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="103" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A103" s="31">
         <v>2018</v>
       </c>
@@ -15863,7 +15846,7 @@
         <v>29</v>
       </c>
       <c r="E103" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F103" s="4">
         <f t="shared" si="2"/>
@@ -15975,7 +15958,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A104" s="31">
         <v>2018</v>
       </c>
@@ -15989,7 +15972,7 @@
         <v>54</v>
       </c>
       <c r="E104" s="33" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="F104" s="4">
         <f t="shared" si="2"/>
@@ -16101,7 +16084,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A105" s="31">
         <v>2018</v>
       </c>
@@ -16115,7 +16098,7 @@
         <v>70</v>
       </c>
       <c r="E105" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F105" s="4" t="str">
         <f t="shared" si="2"/>
@@ -16227,7 +16210,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A106" s="31">
         <v>2018</v>
       </c>
@@ -16241,7 +16224,7 @@
         <v>106</v>
       </c>
       <c r="E106" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F106" s="4" t="str">
         <f t="shared" si="2"/>
@@ -16353,7 +16336,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A107" s="31">
         <v>2018</v>
       </c>
@@ -16367,7 +16350,7 @@
         <v>84</v>
       </c>
       <c r="E107" s="33" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F107" s="4" t="str">
         <f t="shared" si="2"/>
@@ -16479,7 +16462,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A108" s="31">
         <v>2018</v>
       </c>
@@ -16493,7 +16476,7 @@
         <v>40</v>
       </c>
       <c r="E108" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F108" s="4">
         <f t="shared" si="2"/>
@@ -16605,7 +16588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A109" s="31">
         <v>2018</v>
       </c>
@@ -16619,7 +16602,7 @@
         <v>93</v>
       </c>
       <c r="E109" s="33" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F109" s="4">
         <f t="shared" si="2"/>
@@ -16731,7 +16714,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="110" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A110" s="31">
         <v>2018</v>
       </c>
@@ -16745,7 +16728,7 @@
         <v>36</v>
       </c>
       <c r="E110" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F110" s="4">
         <f t="shared" si="2"/>
@@ -16857,7 +16840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A111" s="31">
         <v>2018</v>
       </c>
@@ -16871,7 +16854,7 @@
         <v>106</v>
       </c>
       <c r="E111" s="33" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="F111" s="4">
         <f t="shared" si="2"/>
@@ -16983,7 +16966,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A112" s="31">
         <v>2018</v>
       </c>
@@ -16991,13 +16974,13 @@
         <v>6182</v>
       </c>
       <c r="C112" s="33" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="D112" s="33" t="s">
         <v>54</v>
       </c>
       <c r="E112" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F112" s="4">
         <f t="shared" si="2"/>
@@ -17109,7 +17092,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A113" s="31">
         <v>2018</v>
       </c>
@@ -17123,7 +17106,7 @@
         <v>48</v>
       </c>
       <c r="E113" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F113" s="4">
         <f t="shared" si="2"/>
@@ -17235,7 +17218,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="114" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A114" s="31">
         <v>2018</v>
       </c>
@@ -17249,7 +17232,7 @@
         <v>156</v>
       </c>
       <c r="E114" s="33" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="F114" s="4">
         <f t="shared" si="2"/>
@@ -17361,7 +17344,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A115" s="31">
         <v>2018</v>
       </c>
@@ -17375,7 +17358,7 @@
         <v>40</v>
       </c>
       <c r="E115" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F115" s="4">
         <f t="shared" si="2"/>
@@ -17487,7 +17470,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A116" s="31">
         <v>2018</v>
       </c>
@@ -17501,7 +17484,7 @@
         <v>72</v>
       </c>
       <c r="E116" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F116" s="4">
         <f t="shared" si="2"/>
@@ -17613,7 +17596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A117" s="31">
         <v>2018</v>
       </c>
@@ -17627,7 +17610,7 @@
         <v>93</v>
       </c>
       <c r="E117" s="33" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="F117" s="4">
         <f t="shared" si="2"/>
@@ -17739,7 +17722,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="118" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A118" s="31">
         <v>2018</v>
       </c>
@@ -17753,7 +17736,7 @@
         <v>93</v>
       </c>
       <c r="E118" s="33" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="F118" s="4">
         <f t="shared" si="2"/>
@@ -17865,7 +17848,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A119" s="31">
         <v>2018</v>
       </c>
@@ -17879,7 +17862,7 @@
         <v>104</v>
       </c>
       <c r="E119" s="33" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="F119" s="4">
         <f t="shared" si="2"/>
@@ -17991,7 +17974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A120" s="31">
         <v>2018</v>
       </c>
@@ -18005,7 +17988,7 @@
         <v>79</v>
       </c>
       <c r="E120" s="33" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F120" s="4" t="str">
         <f t="shared" si="2"/>
@@ -18117,7 +18100,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="121" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A121" s="31">
         <v>2018</v>
       </c>
@@ -18125,13 +18108,13 @@
         <v>6709</v>
       </c>
       <c r="C121" s="33" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="D121" s="33" t="s">
         <v>62</v>
       </c>
       <c r="E121" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F121" s="4">
         <f t="shared" si="2"/>
@@ -18243,7 +18226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A122" s="31">
         <v>2018</v>
       </c>
@@ -18257,7 +18240,7 @@
         <v>36</v>
       </c>
       <c r="E122" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F122" s="4">
         <f t="shared" si="2"/>
@@ -18369,7 +18352,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A123" s="31">
         <v>2018</v>
       </c>
@@ -18383,7 +18366,7 @@
         <v>96</v>
       </c>
       <c r="E123" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F123" s="4">
         <f t="shared" si="2"/>
@@ -18495,7 +18478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="124" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A124" s="31">
         <v>2018</v>
       </c>
@@ -18509,7 +18492,7 @@
         <v>40</v>
       </c>
       <c r="E124" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F124" s="4" t="str">
         <f t="shared" si="2"/>
@@ -18621,7 +18604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A125" s="31">
         <v>2018</v>
       </c>
@@ -18635,7 +18618,7 @@
         <v>40</v>
       </c>
       <c r="E125" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F125" s="4">
         <f t="shared" si="2"/>
@@ -18747,7 +18730,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A126" s="31">
         <v>2018</v>
       </c>
@@ -18761,7 +18744,7 @@
         <v>42</v>
       </c>
       <c r="E126" s="33" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="F126" s="4">
         <f t="shared" si="2"/>
@@ -18873,7 +18856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="127" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A127" s="31">
         <v>2018</v>
       </c>
@@ -18887,7 +18870,7 @@
         <v>90</v>
       </c>
       <c r="E127" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F127" s="4" t="str">
         <f t="shared" si="2"/>
@@ -18999,7 +18982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="128" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A128" s="31">
         <v>2018</v>
       </c>
@@ -19013,7 +18996,7 @@
         <v>54</v>
       </c>
       <c r="E128" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F128" s="4" t="str">
         <f t="shared" si="2"/>
@@ -19125,7 +19108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A129" s="31">
         <v>2018</v>
       </c>
@@ -19139,7 +19122,7 @@
         <v>36</v>
       </c>
       <c r="E129" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F129" s="4">
         <f t="shared" si="2"/>
@@ -19251,7 +19234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A130" s="31">
         <v>2018</v>
       </c>
@@ -19265,7 +19248,7 @@
         <v>90</v>
       </c>
       <c r="E130" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F130" s="4" t="str">
         <f t="shared" si="2"/>
@@ -19377,7 +19360,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A131" s="31">
         <v>2018</v>
       </c>
@@ -19391,7 +19374,7 @@
         <v>36</v>
       </c>
       <c r="E131" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F131" s="4">
         <f t="shared" si="2"/>
@@ -19503,7 +19486,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="132" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A132" s="31">
         <v>2018</v>
       </c>
@@ -19517,7 +19500,7 @@
         <v>173</v>
       </c>
       <c r="E132" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F132" s="4">
         <f t="shared" si="2"/>
@@ -19629,7 +19612,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="133" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A133" s="31">
         <v>2018</v>
       </c>
@@ -19643,7 +19626,7 @@
         <v>54</v>
       </c>
       <c r="E133" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F133" s="4" t="str">
         <f t="shared" ref="F133:I196" si="4">IFERROR(SUM(AD133,AI133)*10^3/T133,"")</f>
@@ -19755,7 +19738,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A134" s="31">
         <v>2018</v>
       </c>
@@ -19769,7 +19752,7 @@
         <v>106</v>
       </c>
       <c r="E134" s="33" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="F134" s="4">
         <f t="shared" si="4"/>
@@ -19881,7 +19864,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A135" s="31">
         <v>2018</v>
       </c>
@@ -19889,13 +19872,13 @@
         <v>7752</v>
       </c>
       <c r="C135" s="33" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="D135" s="33" t="s">
         <v>54</v>
       </c>
       <c r="E135" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F135" s="4">
         <f t="shared" si="4"/>
@@ -20007,7 +19990,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A136" s="31">
         <v>2018</v>
       </c>
@@ -20021,7 +20004,7 @@
         <v>93</v>
       </c>
       <c r="E136" s="33" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F136" s="4">
         <f t="shared" si="4"/>
@@ -20133,7 +20116,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="137" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A137" s="31">
         <v>2018</v>
       </c>
@@ -20147,7 +20130,7 @@
         <v>93</v>
       </c>
       <c r="E137" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F137" s="4">
         <f t="shared" si="4"/>
@@ -20259,7 +20242,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="138" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A138" s="31">
         <v>2018</v>
       </c>
@@ -20273,7 +20256,7 @@
         <v>96</v>
       </c>
       <c r="E138" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F138" s="4" t="str">
         <f t="shared" si="4"/>
@@ -20385,7 +20368,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="139" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A139" s="31">
         <v>2018</v>
       </c>
@@ -20399,7 +20382,7 @@
         <v>68</v>
       </c>
       <c r="E139" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F139" s="4">
         <f t="shared" si="4"/>
@@ -20511,7 +20494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A140" s="31">
         <v>2018</v>
       </c>
@@ -20525,7 +20508,7 @@
         <v>40</v>
       </c>
       <c r="E140" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F140" s="4">
         <f t="shared" si="4"/>
@@ -20637,7 +20620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A141" s="31">
         <v>2018</v>
       </c>
@@ -20651,7 +20634,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F141" s="4">
         <f t="shared" si="4"/>
@@ -20763,7 +20746,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A142" s="31">
         <v>2018</v>
       </c>
@@ -20777,7 +20760,7 @@
         <v>38</v>
       </c>
       <c r="E142" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F142" s="4">
         <f t="shared" si="4"/>
@@ -20889,7 +20872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A143" s="31">
         <v>2018</v>
       </c>
@@ -20903,7 +20886,7 @@
         <v>79</v>
       </c>
       <c r="E143" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F143" s="4">
         <f t="shared" si="4"/>
@@ -21015,7 +20998,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="144" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A144" s="31">
         <v>2018</v>
       </c>
@@ -21029,7 +21012,7 @@
         <v>104</v>
       </c>
       <c r="E144" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F144" s="4" t="str">
         <f t="shared" si="4"/>
@@ -21141,7 +21124,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A145" s="31">
         <v>2018</v>
       </c>
@@ -21155,7 +21138,7 @@
         <v>70</v>
       </c>
       <c r="E145" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F145" s="4" t="str">
         <f t="shared" si="4"/>
@@ -21267,7 +21250,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A146" s="31">
         <v>2018</v>
       </c>
@@ -21281,7 +21264,7 @@
         <v>29</v>
       </c>
       <c r="E146" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F146" s="4">
         <f t="shared" si="4"/>
@@ -21393,7 +21376,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="147" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A147" s="31">
         <v>2018</v>
       </c>
@@ -21519,7 +21502,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A148" s="31">
         <v>2018</v>
       </c>
@@ -21533,7 +21516,7 @@
         <v>54</v>
       </c>
       <c r="E148" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F148" s="4">
         <f t="shared" si="4"/>
@@ -21645,7 +21628,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A149" s="31">
         <v>2018</v>
       </c>
@@ -21659,7 +21642,7 @@
         <v>70</v>
       </c>
       <c r="E149" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F149" s="4" t="str">
         <f t="shared" si="4"/>
@@ -21771,7 +21754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="150" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A150" s="31">
         <v>2018</v>
       </c>
@@ -21785,7 +21768,7 @@
         <v>152</v>
       </c>
       <c r="E150" s="33" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="F150" s="4">
         <f t="shared" si="4"/>
@@ -21897,7 +21880,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A151" s="31">
         <v>2018</v>
       </c>
@@ -21911,7 +21894,7 @@
         <v>190</v>
       </c>
       <c r="E151" s="33" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="F151" s="4">
         <f t="shared" si="4"/>
@@ -22023,7 +22006,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A152" s="31">
         <v>2018</v>
       </c>
@@ -22037,7 +22020,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F152" s="4" t="str">
         <f t="shared" si="4"/>
@@ -22149,7 +22132,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A153" s="31">
         <v>2018</v>
       </c>
@@ -22163,7 +22146,7 @@
         <v>106</v>
       </c>
       <c r="E153" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F153" s="4" t="str">
         <f t="shared" si="4"/>
@@ -22275,7 +22258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="154" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A154" s="31">
         <v>2018</v>
       </c>
@@ -22289,7 +22272,7 @@
         <v>68</v>
       </c>
       <c r="E154" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F154" s="4">
         <f t="shared" si="4"/>
@@ -22401,7 +22384,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="155" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A155" s="31">
         <v>2018</v>
       </c>
@@ -22415,7 +22398,7 @@
         <v>68</v>
       </c>
       <c r="E155" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F155" s="4">
         <f t="shared" si="4"/>
@@ -22527,7 +22510,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="156" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A156" s="31">
         <v>2018</v>
       </c>
@@ -22541,7 +22524,7 @@
         <v>68</v>
       </c>
       <c r="E156" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F156" s="4">
         <f t="shared" si="4"/>
@@ -22653,7 +22636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A157" s="31">
         <v>2018</v>
       </c>
@@ -22667,7 +22650,7 @@
         <v>116</v>
       </c>
       <c r="E157" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F157" s="4">
         <f t="shared" si="4"/>
@@ -22779,7 +22762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A158" s="31">
         <v>2018</v>
       </c>
@@ -22793,7 +22776,7 @@
         <v>38</v>
       </c>
       <c r="E158" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F158" s="4">
         <f t="shared" si="4"/>
@@ -22905,7 +22888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A159" s="31">
         <v>2018</v>
       </c>
@@ -22919,7 +22902,7 @@
         <v>40</v>
       </c>
       <c r="E159" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F159" s="4" t="str">
         <f t="shared" si="4"/>
@@ -23031,7 +23014,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="160" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A160" s="31">
         <v>2018</v>
       </c>
@@ -23045,7 +23028,7 @@
         <v>68</v>
       </c>
       <c r="E160" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F160" s="4">
         <f t="shared" si="4"/>
@@ -23157,7 +23140,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="161" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A161" s="31">
         <v>2018</v>
       </c>
@@ -23171,7 +23154,7 @@
         <v>54</v>
       </c>
       <c r="E161" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F161" s="4" t="str">
         <f t="shared" si="4"/>
@@ -23283,7 +23266,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="162" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A162" s="31">
         <v>2018</v>
       </c>
@@ -23297,7 +23280,7 @@
         <v>40</v>
       </c>
       <c r="E162" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F162" s="4">
         <f t="shared" si="4"/>
@@ -23409,7 +23392,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A163" s="31">
         <v>2018</v>
       </c>
@@ -23535,7 +23518,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="164" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A164" s="31">
         <v>2018</v>
       </c>
@@ -23543,13 +23526,13 @@
         <v>9750</v>
       </c>
       <c r="C164" s="33" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D164" s="33" t="s">
         <v>27</v>
       </c>
       <c r="E164" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F164" s="4">
         <f t="shared" si="4"/>
@@ -23661,7 +23644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A165" s="31">
         <v>2018</v>
       </c>
@@ -23675,7 +23658,7 @@
         <v>68</v>
       </c>
       <c r="E165" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F165" s="4" t="str">
         <f t="shared" si="4"/>
@@ -23787,7 +23770,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="166" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A166" s="31">
         <v>2018</v>
       </c>
@@ -23801,7 +23784,7 @@
         <v>29</v>
       </c>
       <c r="E166" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F166" s="4">
         <f t="shared" si="4"/>
@@ -23913,7 +23896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A167" s="31">
         <v>2018</v>
       </c>
@@ -23927,7 +23910,7 @@
         <v>72</v>
       </c>
       <c r="E167" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F167" s="4">
         <f t="shared" si="4"/>
@@ -24039,7 +24022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A168" s="31">
         <v>2018</v>
       </c>
@@ -24053,7 +24036,7 @@
         <v>106</v>
       </c>
       <c r="E168" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F168" s="4">
         <f t="shared" si="4"/>
@@ -24165,7 +24148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A169" s="31">
         <v>2018</v>
       </c>
@@ -24179,7 +24162,7 @@
         <v>72</v>
       </c>
       <c r="E169" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F169" s="4" t="str">
         <f t="shared" si="4"/>
@@ -24291,7 +24274,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="170" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A170" s="31">
         <v>2018</v>
       </c>
@@ -24305,7 +24288,7 @@
         <v>70</v>
       </c>
       <c r="E170" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F170" s="4" t="str">
         <f t="shared" si="4"/>
@@ -24417,7 +24400,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="171" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A171" s="31">
         <v>2018</v>
       </c>
@@ -24431,7 +24414,7 @@
         <v>142</v>
       </c>
       <c r="E171" s="33" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="F171" s="4">
         <f t="shared" si="4"/>
@@ -24543,7 +24526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A172" s="31">
         <v>2018</v>
       </c>
@@ -24557,7 +24540,7 @@
         <v>64</v>
       </c>
       <c r="E172" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F172" s="4">
         <f t="shared" si="4"/>
@@ -24669,7 +24652,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="173" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A173" s="31">
         <v>2018</v>
       </c>
@@ -24683,7 +24666,7 @@
         <v>36</v>
       </c>
       <c r="E173" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F173" s="4" t="str">
         <f t="shared" si="4"/>
@@ -24795,7 +24778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="174" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A174" s="31">
         <v>2018</v>
       </c>
@@ -24809,7 +24792,7 @@
         <v>36</v>
       </c>
       <c r="E174" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F174" s="4" t="str">
         <f t="shared" si="4"/>
@@ -24921,7 +24904,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="175" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A175" s="31">
         <v>2018</v>
       </c>
@@ -24935,7 +24918,7 @@
         <v>62</v>
       </c>
       <c r="E175" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F175" s="4">
         <f>IFERROR(SUM(AD175,AI175)*10^3/T175,"")</f>
@@ -25047,7 +25030,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="176" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A176" s="31">
         <v>2018</v>
       </c>
@@ -25061,7 +25044,7 @@
         <v>93</v>
       </c>
       <c r="E176" s="33" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="F176" s="4">
         <f t="shared" si="4"/>
@@ -25173,7 +25156,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="177" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A177" s="31">
         <v>2018</v>
       </c>
@@ -25181,13 +25164,13 @@
         <v>11018</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="D177" s="33" t="s">
         <v>70</v>
       </c>
       <c r="E177" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F177" s="4">
         <f t="shared" si="4"/>
@@ -25299,7 +25282,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="178" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A178" s="31">
         <v>2018</v>
       </c>
@@ -25313,7 +25296,7 @@
         <v>36</v>
       </c>
       <c r="E178" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F178" s="4">
         <f t="shared" si="4"/>
@@ -25425,7 +25408,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="179" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A179" s="31">
         <v>2018</v>
       </c>
@@ -25439,7 +25422,7 @@
         <v>84</v>
       </c>
       <c r="E179" s="33" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F179" s="4">
         <f t="shared" si="4"/>
@@ -25551,7 +25534,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="180" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A180" s="31">
         <v>2018</v>
       </c>
@@ -25565,7 +25548,7 @@
         <v>42</v>
       </c>
       <c r="E180" s="33" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="F180" s="4" t="str">
         <f t="shared" si="4"/>
@@ -25677,7 +25660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="181" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A181" s="31">
         <v>2018</v>
       </c>
@@ -25691,7 +25674,7 @@
         <v>142</v>
       </c>
       <c r="E181" s="33" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="F181" s="4">
         <f t="shared" si="4"/>
@@ -25803,7 +25786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A182" s="31">
         <v>2018</v>
       </c>
@@ -25817,7 +25800,7 @@
         <v>70</v>
       </c>
       <c r="E182" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F182" s="4" t="str">
         <f t="shared" si="4"/>
@@ -25929,7 +25912,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="183" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A183" s="31">
         <v>2018</v>
       </c>
@@ -25943,7 +25926,7 @@
         <v>152</v>
       </c>
       <c r="E183" s="33" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="F183" s="4" t="str">
         <f t="shared" si="4"/>
@@ -26055,7 +26038,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="184" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A184" s="31">
         <v>2018</v>
       </c>
@@ -26069,7 +26052,7 @@
         <v>219</v>
       </c>
       <c r="E184" s="33" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="F184" s="4">
         <f t="shared" si="4"/>
@@ -26181,7 +26164,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A185" s="31">
         <v>2018</v>
       </c>
@@ -26195,7 +26178,7 @@
         <v>79</v>
       </c>
       <c r="E185" s="33" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F185" s="4">
         <f t="shared" si="4"/>
@@ -26307,7 +26290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A186" s="31">
         <v>2018</v>
       </c>
@@ -26321,7 +26304,7 @@
         <v>38</v>
       </c>
       <c r="E186" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F186" s="4">
         <f t="shared" si="4"/>
@@ -26433,7 +26416,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="187" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A187" s="31">
         <v>2018</v>
       </c>
@@ -26447,7 +26430,7 @@
         <v>64</v>
       </c>
       <c r="E187" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F187" s="4">
         <f t="shared" si="4"/>
@@ -26559,7 +26542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A188" s="31">
         <v>2018</v>
       </c>
@@ -26573,7 +26556,7 @@
         <v>29</v>
       </c>
       <c r="E188" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F188" s="4">
         <f t="shared" si="4"/>
@@ -26685,7 +26668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="189" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A189" s="31">
         <v>2018</v>
       </c>
@@ -26699,7 +26682,7 @@
         <v>25</v>
       </c>
       <c r="E189" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F189" s="4">
         <f t="shared" si="4"/>
@@ -26811,7 +26794,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="190" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A190" s="31">
         <v>2018</v>
       </c>
@@ -26825,7 +26808,7 @@
         <v>38</v>
       </c>
       <c r="E190" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F190" s="4">
         <f t="shared" si="4"/>
@@ -26937,7 +26920,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="191" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A191" s="31">
         <v>2018</v>
       </c>
@@ -26951,7 +26934,7 @@
         <v>36</v>
       </c>
       <c r="E191" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F191" s="4">
         <f t="shared" si="4"/>
@@ -27063,7 +27046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A192" s="31">
         <v>2018</v>
       </c>
@@ -27077,7 +27060,7 @@
         <v>84</v>
       </c>
       <c r="E192" s="33" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F192" s="4">
         <f t="shared" si="4"/>
@@ -27189,7 +27172,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="193" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A193" s="31">
         <v>2018</v>
       </c>
@@ -27203,7 +27186,7 @@
         <v>229</v>
       </c>
       <c r="E193" s="33" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="F193" s="4" t="str">
         <f t="shared" si="4"/>
@@ -27315,7 +27298,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="194" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A194" s="31">
         <v>2018</v>
       </c>
@@ -27329,7 +27312,7 @@
         <v>156</v>
       </c>
       <c r="E194" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F194" s="4" t="str">
         <f t="shared" si="4"/>
@@ -27441,7 +27424,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="195" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A195" s="31">
         <v>2018</v>
       </c>
@@ -27455,7 +27438,7 @@
         <v>77</v>
       </c>
       <c r="E195" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F195" s="4" t="str">
         <f t="shared" si="4"/>
@@ -27567,7 +27550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="196" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A196" s="31">
         <v>2018</v>
       </c>
@@ -27581,7 +27564,7 @@
         <v>219</v>
       </c>
       <c r="E196" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F196" s="4">
         <f t="shared" si="4"/>
@@ -27693,7 +27676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="197" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A197" s="31">
         <v>2018</v>
       </c>
@@ -27707,7 +27690,7 @@
         <v>72</v>
       </c>
       <c r="E197" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F197" s="4" t="str">
         <f t="shared" ref="F197:I260" si="5">IFERROR(SUM(AD197,AI197)*10^3/T197,"")</f>
@@ -27819,7 +27802,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A198" s="31">
         <v>2018</v>
       </c>
@@ -27833,7 +27816,7 @@
         <v>25</v>
       </c>
       <c r="E198" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F198" s="4" t="str">
         <f t="shared" si="5"/>
@@ -27945,7 +27928,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="199" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A199" s="31">
         <v>2018</v>
       </c>
@@ -27953,13 +27936,13 @@
         <v>12265</v>
       </c>
       <c r="C199" s="33" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="D199" s="33" t="s">
         <v>29</v>
       </c>
       <c r="E199" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F199" s="4" t="str">
         <f t="shared" si="5"/>
@@ -28071,7 +28054,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="200" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A200" s="31">
         <v>2018</v>
       </c>
@@ -28085,7 +28068,7 @@
         <v>54</v>
       </c>
       <c r="E200" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F200" s="4" t="str">
         <f t="shared" si="5"/>
@@ -28197,7 +28180,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="201" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A201" s="31">
         <v>2018</v>
       </c>
@@ -28211,7 +28194,7 @@
         <v>77</v>
       </c>
       <c r="E201" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F201" s="4">
         <f t="shared" si="5"/>
@@ -28323,7 +28306,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="202" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A202" s="31">
         <v>2018</v>
       </c>
@@ -28337,7 +28320,7 @@
         <v>38</v>
       </c>
       <c r="E202" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F202" s="4">
         <f t="shared" si="5"/>
@@ -28449,7 +28432,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="203" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A203" s="31">
         <v>2018</v>
       </c>
@@ -28463,7 +28446,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F203" s="4">
         <f t="shared" si="5"/>
@@ -28575,7 +28558,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="204" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A204" s="31">
         <v>2018</v>
       </c>
@@ -28589,7 +28572,7 @@
         <v>64</v>
       </c>
       <c r="E204" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F204" s="4">
         <f t="shared" si="5"/>
@@ -28701,7 +28684,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="205" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A205" s="31">
         <v>2018</v>
       </c>
@@ -28715,7 +28698,7 @@
         <v>116</v>
       </c>
       <c r="E205" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F205" s="4">
         <f t="shared" si="5"/>
@@ -28827,7 +28810,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="206" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A206" s="31">
         <v>2018</v>
       </c>
@@ -28841,7 +28824,7 @@
         <v>89</v>
       </c>
       <c r="E206" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F206" s="4">
         <f t="shared" si="5"/>
@@ -28953,7 +28936,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="207" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A207" s="31">
         <v>2018</v>
       </c>
@@ -28967,7 +28950,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F207" s="4">
         <f t="shared" si="5"/>
@@ -29079,7 +29062,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="208" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A208" s="31">
         <v>2018</v>
       </c>
@@ -29087,13 +29070,13 @@
         <v>12439</v>
       </c>
       <c r="C208" s="33" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="D208" s="33" t="s">
         <v>190</v>
       </c>
       <c r="E208" s="33" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="F208" s="4">
         <f t="shared" si="5"/>
@@ -29205,7 +29188,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="209" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A209" s="31">
         <v>2018</v>
       </c>
@@ -29219,7 +29202,7 @@
         <v>156</v>
       </c>
       <c r="E209" s="33" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="F209" s="4">
         <f t="shared" si="5"/>
@@ -29331,7 +29314,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="210" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A210" s="31">
         <v>2018</v>
       </c>
@@ -29345,7 +29328,7 @@
         <v>40</v>
       </c>
       <c r="E210" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F210" s="4" t="str">
         <f t="shared" si="5"/>
@@ -29457,7 +29440,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A211" s="31">
         <v>2018</v>
       </c>
@@ -29471,7 +29454,7 @@
         <v>72</v>
       </c>
       <c r="E211" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F211" s="4" t="str">
         <f t="shared" si="5"/>
@@ -29583,7 +29566,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="212" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A212" s="31">
         <v>2018</v>
       </c>
@@ -29597,7 +29580,7 @@
         <v>70</v>
       </c>
       <c r="E212" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F212" s="4" t="str">
         <f t="shared" si="5"/>
@@ -29709,7 +29692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="213" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A213" s="31">
         <v>2018</v>
       </c>
@@ -29723,7 +29706,7 @@
         <v>190</v>
       </c>
       <c r="E213" s="33" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="F213" s="4">
         <f t="shared" si="5"/>
@@ -29835,7 +29818,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="214" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A214" s="31">
         <v>2018</v>
       </c>
@@ -29849,7 +29832,7 @@
         <v>36</v>
       </c>
       <c r="E214" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F214" s="4">
         <f t="shared" si="5"/>
@@ -29961,7 +29944,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="215" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A215" s="31">
         <v>2018</v>
       </c>
@@ -29975,7 +29958,7 @@
         <v>96</v>
       </c>
       <c r="E215" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F215" s="4" t="str">
         <f t="shared" si="5"/>
@@ -30087,7 +30070,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="216" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A216" s="31">
         <v>2018</v>
       </c>
@@ -30101,7 +30084,7 @@
         <v>48</v>
       </c>
       <c r="E216" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F216" s="4" t="str">
         <f t="shared" si="5"/>
@@ -30213,7 +30196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="217" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A217" s="31">
         <v>2018</v>
       </c>
@@ -30227,7 +30210,7 @@
         <v>248</v>
       </c>
       <c r="E217" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F217" s="4" t="str">
         <f t="shared" si="5"/>
@@ -30339,7 +30322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A218" s="31">
         <v>2018</v>
       </c>
@@ -30353,7 +30336,7 @@
         <v>106</v>
       </c>
       <c r="E218" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F218" s="4">
         <f t="shared" si="5"/>
@@ -30465,7 +30448,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="219" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A219" s="31">
         <v>2018</v>
       </c>
@@ -30479,7 +30462,7 @@
         <v>42</v>
       </c>
       <c r="E219" s="33" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="F219" s="4">
         <f t="shared" si="5"/>
@@ -30591,7 +30574,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="220" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A220" s="31">
         <v>2018</v>
       </c>
@@ -30605,7 +30588,7 @@
         <v>44</v>
       </c>
       <c r="E220" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F220" s="4" t="str">
         <f t="shared" si="5"/>
@@ -30717,7 +30700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A221" s="31">
         <v>2018</v>
       </c>
@@ -30731,7 +30714,7 @@
         <v>36</v>
       </c>
       <c r="E221" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F221" s="4">
         <f t="shared" si="5"/>
@@ -30843,7 +30826,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="222" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A222" s="31">
         <v>2018</v>
       </c>
@@ -30857,7 +30840,7 @@
         <v>36</v>
       </c>
       <c r="E222" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F222" s="4" t="str">
         <f t="shared" si="5"/>
@@ -30969,7 +30952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A223" s="31">
         <v>2018</v>
       </c>
@@ -30983,7 +30966,7 @@
         <v>64</v>
       </c>
       <c r="E223" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F223" s="4">
         <f t="shared" si="5"/>
@@ -31095,7 +31078,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="224" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A224" s="31">
         <v>2018</v>
       </c>
@@ -31109,7 +31092,7 @@
         <v>104</v>
       </c>
       <c r="E224" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F224" s="4">
         <f t="shared" si="5"/>
@@ -31221,7 +31204,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="225" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A225" s="31">
         <v>2018</v>
       </c>
@@ -31235,7 +31218,7 @@
         <v>70</v>
       </c>
       <c r="E225" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F225" s="4" t="str">
         <f t="shared" si="5"/>
@@ -31347,7 +31330,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A226" s="31">
         <v>2018</v>
       </c>
@@ -31361,7 +31344,7 @@
         <v>258</v>
       </c>
       <c r="E226" s="33" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F226" s="4">
         <f t="shared" si="5"/>
@@ -31473,7 +31456,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="227" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A227" s="31">
         <v>2018</v>
       </c>
@@ -31481,13 +31464,13 @@
         <v>13441</v>
       </c>
       <c r="C227" s="33" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="D227" s="33" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="E227" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F227" s="4">
         <f t="shared" si="5"/>
@@ -31599,7 +31582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="228" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A228" s="31">
         <v>2018</v>
       </c>
@@ -31607,13 +31590,13 @@
         <v>13478</v>
       </c>
       <c r="C228" s="33" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="D228" s="33" t="s">
         <v>259</v>
       </c>
       <c r="E228" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F228" s="4">
         <f t="shared" si="5"/>
@@ -31725,7 +31708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="229" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A229" s="31">
         <v>2018</v>
       </c>
@@ -31739,7 +31722,7 @@
         <v>36</v>
       </c>
       <c r="E229" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F229" s="4">
         <f t="shared" si="5"/>
@@ -31851,7 +31834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A230" s="31">
         <v>2018</v>
       </c>
@@ -31865,7 +31848,7 @@
         <v>93</v>
       </c>
       <c r="E230" s="33" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="F230" s="4">
         <f t="shared" si="5"/>
@@ -31977,7 +31960,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="231" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A231" s="31">
         <v>2018</v>
       </c>
@@ -31991,7 +31974,7 @@
         <v>84</v>
       </c>
       <c r="E231" s="33" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F231" s="4">
         <f t="shared" si="5"/>
@@ -32103,7 +32086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="232" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A232" s="31">
         <v>2018</v>
       </c>
@@ -32117,7 +32100,7 @@
         <v>84</v>
       </c>
       <c r="E232" s="33" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F232" s="4">
         <f t="shared" si="5"/>
@@ -32229,7 +32212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="233" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A233" s="31">
         <v>2018</v>
       </c>
@@ -32243,7 +32226,7 @@
         <v>79</v>
       </c>
       <c r="E233" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F233" s="4">
         <f t="shared" si="5"/>
@@ -32355,7 +32338,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="234" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A234" s="31">
         <v>2018</v>
       </c>
@@ -32369,7 +32352,7 @@
         <v>25</v>
       </c>
       <c r="E234" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F234" s="4">
         <f t="shared" si="5"/>
@@ -32481,7 +32464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="235" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A235" s="31">
         <v>2018</v>
       </c>
@@ -32495,7 +32478,7 @@
         <v>70</v>
       </c>
       <c r="E235" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F235" s="4" t="str">
         <f t="shared" si="5"/>
@@ -32607,7 +32590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="236" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A236" s="31">
         <v>2018</v>
       </c>
@@ -32621,7 +32604,7 @@
         <v>48</v>
       </c>
       <c r="E236" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F236" s="4">
         <f t="shared" si="5"/>
@@ -32733,7 +32716,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="237" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A237" s="31">
         <v>2018</v>
       </c>
@@ -32747,7 +32730,7 @@
         <v>79</v>
       </c>
       <c r="E237" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F237" s="4">
         <f t="shared" si="5"/>
@@ -32859,7 +32842,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="238" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A238" s="31">
         <v>2018</v>
       </c>
@@ -32873,7 +32856,7 @@
         <v>79</v>
       </c>
       <c r="E238" s="33" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F238" s="4">
         <f t="shared" si="5"/>
@@ -32985,7 +32968,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="239" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A239" s="31">
         <v>2018</v>
       </c>
@@ -32999,7 +32982,7 @@
         <v>106</v>
       </c>
       <c r="E239" s="33" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="F239" s="4">
         <f t="shared" si="5"/>
@@ -33111,7 +33094,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A240" s="31">
         <v>2018</v>
       </c>
@@ -33125,7 +33108,7 @@
         <v>70</v>
       </c>
       <c r="E240" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F240" s="4" t="str">
         <f t="shared" si="5"/>
@@ -33237,7 +33220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A241" s="31">
         <v>2018</v>
       </c>
@@ -33251,7 +33234,7 @@
         <v>70</v>
       </c>
       <c r="E241" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F241" s="4">
         <f t="shared" si="5"/>
@@ -33363,7 +33346,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="242" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A242" s="31">
         <v>2018</v>
       </c>
@@ -33377,7 +33360,7 @@
         <v>25</v>
       </c>
       <c r="E242" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F242" s="4">
         <f t="shared" si="5"/>
@@ -33489,7 +33472,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="243" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A243" s="31">
         <v>2018</v>
       </c>
@@ -33503,7 +33486,7 @@
         <v>29</v>
       </c>
       <c r="E243" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F243" s="4">
         <f t="shared" si="5"/>
@@ -33615,7 +33598,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="244" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A244" s="31">
         <v>2018</v>
       </c>
@@ -33629,7 +33612,7 @@
         <v>36</v>
       </c>
       <c r="E244" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F244" s="4">
         <f t="shared" si="5"/>
@@ -33741,7 +33724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="245" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A245" s="31">
         <v>2018</v>
       </c>
@@ -33755,7 +33738,7 @@
         <v>77</v>
       </c>
       <c r="E245" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F245" s="4">
         <f t="shared" si="5"/>
@@ -33867,7 +33850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="246" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A246" s="31">
         <v>2018</v>
       </c>
@@ -33881,7 +33864,7 @@
         <v>64</v>
       </c>
       <c r="E246" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F246" s="4">
         <f t="shared" si="5"/>
@@ -33993,7 +33976,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A247" s="31">
         <v>2018</v>
       </c>
@@ -34007,7 +33990,7 @@
         <v>38</v>
       </c>
       <c r="E247" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F247" s="4">
         <f t="shared" si="5"/>
@@ -34119,7 +34102,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="248" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A248" s="31">
         <v>2018</v>
       </c>
@@ -34133,7 +34116,7 @@
         <v>29</v>
       </c>
       <c r="E248" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F248" s="4" t="str">
         <f t="shared" si="5"/>
@@ -34245,7 +34228,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="249" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A249" s="31">
         <v>2018</v>
       </c>
@@ -34259,7 +34242,7 @@
         <v>90</v>
       </c>
       <c r="E249" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F249" s="4" t="str">
         <f t="shared" si="5"/>
@@ -34371,7 +34354,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="250" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A250" s="31">
         <v>2018</v>
       </c>
@@ -34385,7 +34368,7 @@
         <v>111</v>
       </c>
       <c r="E250" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F250" s="4">
         <f t="shared" si="5"/>
@@ -34497,7 +34480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A251" s="31">
         <v>2018</v>
       </c>
@@ -34511,7 +34494,7 @@
         <v>29</v>
       </c>
       <c r="E251" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F251" s="4">
         <f t="shared" si="5"/>
@@ -34623,7 +34606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A252" s="31">
         <v>2018</v>
       </c>
@@ -34637,7 +34620,7 @@
         <v>96</v>
       </c>
       <c r="E252" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F252" s="4" t="str">
         <f t="shared" si="5"/>
@@ -34749,7 +34732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="253" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A253" s="31">
         <v>2018</v>
       </c>
@@ -34763,7 +34746,7 @@
         <v>48</v>
       </c>
       <c r="E253" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F253" s="4" t="str">
         <f t="shared" si="5"/>
@@ -34875,7 +34858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A254" s="31">
         <v>2018</v>
       </c>
@@ -34889,7 +34872,7 @@
         <v>90</v>
       </c>
       <c r="E254" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F254" s="4">
         <f t="shared" si="5"/>
@@ -35001,7 +34984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A255" s="31">
         <v>2018</v>
       </c>
@@ -35015,7 +34998,7 @@
         <v>70</v>
       </c>
       <c r="E255" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F255" s="4">
         <f t="shared" si="5"/>
@@ -35127,7 +35110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A256" s="31">
         <v>2018</v>
       </c>
@@ -35135,13 +35118,13 @@
         <v>14132</v>
       </c>
       <c r="C256" s="33" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="D256" s="33" t="s">
         <v>38</v>
       </c>
       <c r="E256" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F256" s="4">
         <f t="shared" si="5"/>
@@ -35253,7 +35236,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="257" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A257" s="31">
         <v>2018</v>
       </c>
@@ -35267,7 +35250,7 @@
         <v>84</v>
       </c>
       <c r="E257" s="33" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F257" s="4">
         <f t="shared" si="5"/>
@@ -35379,7 +35362,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="258" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A258" s="31">
         <v>2018</v>
       </c>
@@ -35505,7 +35488,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="259" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A259" s="31">
         <v>2018</v>
       </c>
@@ -35519,7 +35502,7 @@
         <v>36</v>
       </c>
       <c r="E259" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F259" s="4">
         <f t="shared" si="5"/>
@@ -35631,7 +35614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A260" s="31">
         <v>2018</v>
       </c>
@@ -35645,7 +35628,7 @@
         <v>38</v>
       </c>
       <c r="E260" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F260" s="4">
         <f t="shared" si="5"/>
@@ -35757,7 +35740,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="261" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A261" s="31">
         <v>2018</v>
       </c>
@@ -35771,7 +35754,7 @@
         <v>38</v>
       </c>
       <c r="E261" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F261" s="4">
         <f t="shared" ref="F261:I324" si="7">IFERROR(SUM(AD261,AI261)*10^3/T261,"")</f>
@@ -35883,7 +35866,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="262" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A262" s="31">
         <v>2018</v>
       </c>
@@ -35897,7 +35880,7 @@
         <v>36</v>
       </c>
       <c r="E262" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F262" s="4">
         <f t="shared" si="7"/>
@@ -36009,7 +35992,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="263" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A263" s="31">
         <v>2018</v>
       </c>
@@ -36017,13 +36000,13 @@
         <v>14328</v>
       </c>
       <c r="C263" s="33" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D263" s="33" t="s">
         <v>42</v>
       </c>
       <c r="E263" s="33" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F263" s="4">
         <f t="shared" si="7"/>
@@ -36135,7 +36118,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="264" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A264" s="31">
         <v>2018</v>
       </c>
@@ -36149,7 +36132,7 @@
         <v>152</v>
       </c>
       <c r="E264" s="33" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F264" s="4" t="str">
         <f t="shared" si="7"/>
@@ -36261,7 +36244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A265" s="31">
         <v>2018</v>
       </c>
@@ -36275,7 +36258,7 @@
         <v>190</v>
       </c>
       <c r="E265" s="33" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="F265" s="4" t="str">
         <f t="shared" si="7"/>
@@ -36387,7 +36370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A266" s="31">
         <v>2018</v>
       </c>
@@ -36401,7 +36384,7 @@
         <v>291</v>
       </c>
       <c r="E266" s="33" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F266" s="4">
         <f t="shared" si="7"/>
@@ -36513,7 +36496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A267" s="31">
         <v>2018</v>
       </c>
@@ -36639,7 +36622,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="268" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A268" s="31">
         <v>2018</v>
       </c>
@@ -36653,7 +36636,7 @@
         <v>70</v>
       </c>
       <c r="E268" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F268" s="4" t="str">
         <f t="shared" si="7"/>
@@ -36765,7 +36748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A269" s="31">
         <v>2018</v>
       </c>
@@ -36779,7 +36762,7 @@
         <v>36</v>
       </c>
       <c r="E269" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F269" s="4">
         <f t="shared" si="7"/>
@@ -36891,7 +36874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A270" s="31">
         <v>2018</v>
       </c>
@@ -37017,7 +37000,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="271" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A271" s="31">
         <v>2018</v>
       </c>
@@ -37025,13 +37008,13 @@
         <v>14715</v>
       </c>
       <c r="C271" s="33" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="D271" s="33" t="s">
         <v>89</v>
       </c>
       <c r="E271" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F271" s="4" t="str">
         <f t="shared" si="7"/>
@@ -37143,7 +37126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="272" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A272" s="31">
         <v>2018</v>
       </c>
@@ -37157,7 +37140,7 @@
         <v>89</v>
       </c>
       <c r="E272" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F272" s="4">
         <f t="shared" si="7"/>
@@ -37269,7 +37252,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="273" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A273" s="31">
         <v>2018</v>
       </c>
@@ -37283,7 +37266,7 @@
         <v>79</v>
       </c>
       <c r="E273" s="33" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F273" s="4" t="str">
         <f t="shared" si="7"/>
@@ -37395,7 +37378,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="274" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A274" s="31">
         <v>2018</v>
       </c>
@@ -37409,7 +37392,7 @@
         <v>89</v>
       </c>
       <c r="E274" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F274" s="4">
         <f t="shared" si="7"/>
@@ -37521,7 +37504,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="275" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A275" s="31">
         <v>2018</v>
       </c>
@@ -37535,7 +37518,7 @@
         <v>79</v>
       </c>
       <c r="E275" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F275" s="4">
         <f t="shared" si="7"/>
@@ -37647,7 +37630,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="276" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A276" s="31">
         <v>2018</v>
       </c>
@@ -37661,7 +37644,7 @@
         <v>29</v>
       </c>
       <c r="E276" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F276" s="4">
         <f t="shared" si="7"/>
@@ -37773,7 +37756,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="277" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A277" s="31">
         <v>2018</v>
       </c>
@@ -37781,13 +37764,13 @@
         <v>15188</v>
       </c>
       <c r="C277" s="33" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="D277" s="33" t="s">
         <v>70</v>
       </c>
       <c r="E277" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F277" s="4" t="str">
         <f t="shared" si="7"/>
@@ -37899,7 +37882,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="278" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A278" s="31">
         <v>2018</v>
       </c>
@@ -37913,7 +37896,7 @@
         <v>190</v>
       </c>
       <c r="E278" s="33" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="F278" s="4">
         <f t="shared" si="7"/>
@@ -38025,7 +38008,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="279" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A279" s="31">
         <v>2018</v>
       </c>
@@ -38039,7 +38022,7 @@
         <v>303</v>
       </c>
       <c r="E279" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F279" s="4">
         <f t="shared" si="7"/>
@@ -38151,7 +38134,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="280" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A280" s="31">
         <v>2018</v>
       </c>
@@ -38165,7 +38148,7 @@
         <v>23</v>
       </c>
       <c r="E280" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F280" s="4">
         <f t="shared" si="7"/>
@@ -38277,7 +38260,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="281" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A281" s="31">
         <v>2018</v>
       </c>
@@ -38291,7 +38274,7 @@
         <v>29</v>
       </c>
       <c r="E281" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F281" s="4">
         <f t="shared" si="7"/>
@@ -38403,7 +38386,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="282" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A282" s="31">
         <v>2018</v>
       </c>
@@ -38417,7 +38400,7 @@
         <v>29</v>
       </c>
       <c r="E282" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F282" s="4">
         <f t="shared" si="7"/>
@@ -38529,7 +38512,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="283" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A283" s="31">
         <v>2018</v>
       </c>
@@ -38543,7 +38526,7 @@
         <v>36</v>
       </c>
       <c r="E283" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F283" s="4">
         <f t="shared" si="7"/>
@@ -38655,7 +38638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A284" s="31">
         <v>2018</v>
       </c>
@@ -38669,7 +38652,7 @@
         <v>25</v>
       </c>
       <c r="E284" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F284" s="4">
         <f t="shared" si="7"/>
@@ -38781,7 +38764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A285" s="31">
         <v>2018</v>
       </c>
@@ -38795,7 +38778,7 @@
         <v>104</v>
       </c>
       <c r="E285" s="33" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="F285" s="4">
         <f t="shared" si="7"/>
@@ -38907,7 +38890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A286" s="31">
         <v>2018</v>
       </c>
@@ -38921,7 +38904,7 @@
         <v>68</v>
       </c>
       <c r="E286" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F286" s="4">
         <f t="shared" si="7"/>
@@ -39033,7 +39016,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="287" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A287" s="31">
         <v>2018</v>
       </c>
@@ -39047,7 +39030,7 @@
         <v>145</v>
       </c>
       <c r="E287" s="33" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F287" s="4">
         <f t="shared" si="7"/>
@@ -39159,7 +39142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A288" s="31">
         <v>2018</v>
       </c>
@@ -39173,7 +39156,7 @@
         <v>90</v>
       </c>
       <c r="E288" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F288" s="4" t="str">
         <f t="shared" si="7"/>
@@ -39285,7 +39268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A289" s="31">
         <v>2018</v>
       </c>
@@ -39299,7 +39282,7 @@
         <v>51</v>
       </c>
       <c r="E289" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F289" s="4">
         <f t="shared" si="7"/>
@@ -39411,7 +39394,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="290" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A290" s="31">
         <v>2018</v>
       </c>
@@ -39425,7 +39408,7 @@
         <v>25</v>
       </c>
       <c r="E290" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F290" s="4" t="str">
         <f t="shared" si="7"/>
@@ -39537,7 +39520,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="291" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A291" s="31">
         <v>2018</v>
       </c>
@@ -39551,7 +39534,7 @@
         <v>79</v>
       </c>
       <c r="E291" s="33" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F291" s="4" t="str">
         <f t="shared" si="7"/>
@@ -39663,7 +39646,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="292" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A292" s="31">
         <v>2018</v>
       </c>
@@ -39677,7 +39660,7 @@
         <v>40</v>
       </c>
       <c r="E292" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F292" s="4" t="str">
         <f t="shared" si="7"/>
@@ -39789,7 +39772,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="293" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A293" s="31">
         <v>2018</v>
       </c>
@@ -39803,7 +39786,7 @@
         <v>90</v>
       </c>
       <c r="E293" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F293" s="4" t="str">
         <f t="shared" si="7"/>
@@ -39915,7 +39898,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="294" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A294" s="31">
         <v>2018</v>
       </c>
@@ -39929,7 +39912,7 @@
         <v>111</v>
       </c>
       <c r="E294" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F294" s="4" t="str">
         <f t="shared" si="7"/>
@@ -40041,7 +40024,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="295" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A295" s="31">
         <v>2018</v>
       </c>
@@ -40055,7 +40038,7 @@
         <v>29</v>
       </c>
       <c r="E295" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F295" s="4">
         <f t="shared" si="7"/>
@@ -40167,7 +40150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="296" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A296" s="31">
         <v>2018</v>
       </c>
@@ -40175,13 +40158,13 @@
         <v>16101</v>
       </c>
       <c r="C296" s="33" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="D296" s="33" t="s">
         <v>79</v>
       </c>
       <c r="E296" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F296" s="4">
         <f t="shared" si="7"/>
@@ -40293,7 +40276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="297" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A297" s="31">
         <v>2018</v>
       </c>
@@ -40307,7 +40290,7 @@
         <v>36</v>
       </c>
       <c r="E297" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F297" s="4">
         <f t="shared" si="7"/>
@@ -40419,7 +40402,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="298" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A298" s="31">
         <v>2018</v>
       </c>
@@ -40433,7 +40416,7 @@
         <v>84</v>
       </c>
       <c r="E298" s="33" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F298" s="4">
         <f t="shared" si="7"/>
@@ -40545,7 +40528,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="299" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A299" s="31">
         <v>2018</v>
       </c>
@@ -40559,7 +40542,7 @@
         <v>72</v>
       </c>
       <c r="E299" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F299" s="4" t="str">
         <f t="shared" si="7"/>
@@ -40671,7 +40654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="300" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A300" s="31">
         <v>2018</v>
       </c>
@@ -40685,7 +40668,7 @@
         <v>36</v>
       </c>
       <c r="E300" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F300" s="4">
         <f t="shared" si="7"/>
@@ -40797,7 +40780,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A301" s="31">
         <v>2018</v>
       </c>
@@ -40811,7 +40794,7 @@
         <v>42</v>
       </c>
       <c r="E301" s="33" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="F301" s="4">
         <f t="shared" si="7"/>
@@ -40923,7 +40906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="302" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A302" s="31">
         <v>2018</v>
       </c>
@@ -40937,7 +40920,7 @@
         <v>79</v>
       </c>
       <c r="E302" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F302" s="4">
         <f t="shared" si="7"/>
@@ -41049,7 +41032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A303" s="31">
         <v>2018</v>
       </c>
@@ -41063,7 +41046,7 @@
         <v>42</v>
       </c>
       <c r="E303" s="33" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="F303" s="4">
         <f t="shared" si="7"/>
@@ -41175,7 +41158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A304" s="31">
         <v>2018</v>
       </c>
@@ -41189,7 +41172,7 @@
         <v>46</v>
       </c>
       <c r="E304" s="33" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F304" s="4">
         <f t="shared" si="7"/>
@@ -41301,7 +41284,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="305" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A305" s="31">
         <v>2018</v>
       </c>
@@ -41315,7 +41298,7 @@
         <v>54</v>
       </c>
       <c r="E305" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F305" s="4">
         <f t="shared" si="7"/>
@@ -41427,7 +41410,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="306" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A306" s="31">
         <v>2018</v>
       </c>
@@ -41553,7 +41536,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="307" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A307" s="31">
         <v>2018</v>
       </c>
@@ -41567,7 +41550,7 @@
         <v>42</v>
       </c>
       <c r="E307" s="33" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F307" s="4">
         <f t="shared" si="7"/>
@@ -41679,7 +41662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="308" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A308" s="31">
         <v>2018</v>
       </c>
@@ -41693,7 +41676,7 @@
         <v>54</v>
       </c>
       <c r="E308" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F308" s="4" t="str">
         <f t="shared" si="7"/>
@@ -41805,7 +41788,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="309" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A309" s="31">
         <v>2018</v>
       </c>
@@ -41819,7 +41802,7 @@
         <v>40</v>
       </c>
       <c r="E309" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F309" s="4" t="str">
         <f t="shared" si="7"/>
@@ -41931,7 +41914,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="310" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A310" s="31">
         <v>2018</v>
       </c>
@@ -41945,7 +41928,7 @@
         <v>29</v>
       </c>
       <c r="E310" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F310" s="4">
         <f t="shared" si="7"/>
@@ -42057,7 +42040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="311" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A311" s="31">
         <v>2018</v>
       </c>
@@ -42071,7 +42054,7 @@
         <v>106</v>
       </c>
       <c r="E311" s="33" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="F311" s="4" t="str">
         <f t="shared" si="7"/>
@@ -42183,7 +42166,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="312" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A312" s="31">
         <v>2018</v>
       </c>
@@ -42197,7 +42180,7 @@
         <v>72</v>
       </c>
       <c r="E312" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F312" s="4">
         <f t="shared" si="7"/>
@@ -42309,7 +42292,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="313" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A313" s="31">
         <v>2018</v>
       </c>
@@ -42323,7 +42306,7 @@
         <v>40</v>
       </c>
       <c r="E313" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F313" s="4">
         <f t="shared" si="7"/>
@@ -42435,7 +42418,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="314" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A314" s="31">
         <v>2018</v>
       </c>
@@ -42449,7 +42432,7 @@
         <v>72</v>
       </c>
       <c r="E314" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F314" s="4" t="str">
         <f t="shared" si="7"/>
@@ -42561,7 +42544,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="315" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A315" s="31">
         <v>2018</v>
       </c>
@@ -42575,7 +42558,7 @@
         <v>38</v>
       </c>
       <c r="E315" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F315" s="4">
         <f t="shared" si="7"/>
@@ -42687,7 +42670,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="316" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A316" s="31">
         <v>2018</v>
       </c>
@@ -42701,7 +42684,7 @@
         <v>36</v>
       </c>
       <c r="E316" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F316" s="4">
         <f t="shared" si="7"/>
@@ -42813,7 +42796,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="317" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A317" s="31">
         <v>2018</v>
       </c>
@@ -42827,7 +42810,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F317" s="4">
         <f t="shared" si="7"/>
@@ -42939,7 +42922,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="318" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A318" s="31">
         <v>2018</v>
       </c>
@@ -42953,7 +42936,7 @@
         <v>25</v>
       </c>
       <c r="E318" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F318" s="4">
         <f t="shared" si="7"/>
@@ -43065,7 +43048,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="319" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A319" s="31">
         <v>2018</v>
       </c>
@@ -43079,7 +43062,7 @@
         <v>258</v>
       </c>
       <c r="E319" s="33" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F319" s="4">
         <f t="shared" si="7"/>
@@ -43191,7 +43174,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="320" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A320" s="31">
         <v>2018</v>
       </c>
@@ -43199,13 +43182,13 @@
         <v>17252</v>
       </c>
       <c r="C320" s="33" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="D320" s="33" t="s">
         <v>248</v>
       </c>
       <c r="E320" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F320" s="4" t="str">
         <f t="shared" si="7"/>
@@ -43317,7 +43300,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="321" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A321" s="31">
         <v>2018</v>
       </c>
@@ -43331,7 +43314,7 @@
         <v>38</v>
       </c>
       <c r="E321" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F321" s="4">
         <f t="shared" si="7"/>
@@ -43443,7 +43426,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="322" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A322" s="31">
         <v>2018</v>
       </c>
@@ -43451,13 +43434,13 @@
         <v>17267</v>
       </c>
       <c r="C322" s="33" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D322" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E322" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F322" s="4" t="str">
         <f t="shared" si="7"/>
@@ -43569,7 +43552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A323" s="31">
         <v>2018</v>
       </c>
@@ -43577,13 +43560,13 @@
         <v>17267</v>
       </c>
       <c r="C323" s="33" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D323" s="33" t="s">
         <v>64</v>
       </c>
       <c r="E323" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F323" s="4" t="str">
         <f t="shared" si="7"/>
@@ -43695,7 +43678,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="324" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A324" s="31">
         <v>2018</v>
       </c>
@@ -43703,13 +43686,13 @@
         <v>17539</v>
       </c>
       <c r="C324" s="33" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D324" s="33" t="s">
         <v>62</v>
       </c>
       <c r="E324" s="33" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="F324" s="4" t="str">
         <f t="shared" si="7"/>
@@ -43821,7 +43804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="325" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A325" s="31">
         <v>2018</v>
       </c>
@@ -43947,7 +43930,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="326" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A326" s="31">
         <v>2018</v>
       </c>
@@ -43961,7 +43944,7 @@
         <v>70</v>
       </c>
       <c r="E326" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F326" s="4" t="str">
         <f t="shared" si="8"/>
@@ -44073,7 +44056,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="327" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A327" s="31">
         <v>2018</v>
       </c>
@@ -44087,7 +44070,7 @@
         <v>54</v>
       </c>
       <c r="E327" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F327" s="4" t="str">
         <f t="shared" si="8"/>
@@ -44199,7 +44182,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="328" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A328" s="31">
         <v>2018</v>
       </c>
@@ -44213,7 +44196,7 @@
         <v>79</v>
       </c>
       <c r="E328" s="33" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F328" s="4">
         <f t="shared" si="8"/>
@@ -44325,7 +44308,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="329" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A329" s="31">
         <v>2018</v>
       </c>
@@ -44339,7 +44322,7 @@
         <v>70</v>
       </c>
       <c r="E329" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F329" s="4" t="str">
         <f t="shared" si="8"/>
@@ -44451,7 +44434,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="330" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A330" s="31">
         <v>2018</v>
       </c>
@@ -44459,13 +44442,13 @@
         <v>17599</v>
       </c>
       <c r="C330" s="33" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="D330" s="33" t="s">
         <v>68</v>
       </c>
       <c r="E330" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F330" s="4">
         <f t="shared" si="8"/>
@@ -44577,7 +44560,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="331" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A331" s="31">
         <v>2018</v>
       </c>
@@ -44591,7 +44574,7 @@
         <v>42</v>
       </c>
       <c r="E331" s="33" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F331" s="4">
         <f t="shared" si="8"/>
@@ -44703,7 +44686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="332" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A332" s="31">
         <v>2018</v>
       </c>
@@ -44717,7 +44700,7 @@
         <v>42</v>
       </c>
       <c r="E332" s="33" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F332" s="4" t="str">
         <f t="shared" si="8"/>
@@ -44829,7 +44812,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="333" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A333" s="31">
         <v>2018</v>
       </c>
@@ -44843,7 +44826,7 @@
         <v>68</v>
       </c>
       <c r="E333" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F333" s="4">
         <f t="shared" si="8"/>
@@ -44955,7 +44938,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="334" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A334" s="31">
         <v>2018</v>
       </c>
@@ -44969,7 +44952,7 @@
         <v>23</v>
       </c>
       <c r="E334" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F334" s="4">
         <f t="shared" si="8"/>
@@ -45081,7 +45064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A335" s="31">
         <v>2018</v>
       </c>
@@ -45095,7 +45078,7 @@
         <v>48</v>
       </c>
       <c r="E335" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F335" s="4" t="str">
         <f t="shared" si="8"/>
@@ -45207,7 +45190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A336" s="31">
         <v>2018</v>
       </c>
@@ -45221,7 +45204,7 @@
         <v>259</v>
       </c>
       <c r="E336" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F336" s="4" t="str">
         <f t="shared" si="8"/>
@@ -45333,7 +45316,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="337" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A337" s="31">
         <v>2018</v>
       </c>
@@ -45347,7 +45330,7 @@
         <v>70</v>
       </c>
       <c r="E337" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F337" s="4" t="str">
         <f t="shared" si="8"/>
@@ -45459,7 +45442,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="338" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A338" s="31">
         <v>2018</v>
       </c>
@@ -45473,7 +45456,7 @@
         <v>48</v>
       </c>
       <c r="E338" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F338" s="4" t="str">
         <f t="shared" si="8"/>
@@ -45585,7 +45568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A339" s="31">
         <v>2018</v>
       </c>
@@ -45599,7 +45582,7 @@
         <v>54</v>
       </c>
       <c r="E339" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F339" s="4" t="str">
         <f t="shared" si="8"/>
@@ -45711,7 +45694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A340" s="31">
         <v>2018</v>
       </c>
@@ -45725,7 +45708,7 @@
         <v>145</v>
       </c>
       <c r="E340" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F340" s="4">
         <f t="shared" si="8"/>
@@ -45837,7 +45820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A341" s="31">
         <v>2018</v>
       </c>
@@ -45851,7 +45834,7 @@
         <v>54</v>
       </c>
       <c r="E341" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F341" s="4">
         <f t="shared" si="8"/>
@@ -45963,7 +45946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A342" s="31">
         <v>2018</v>
       </c>
@@ -45971,13 +45954,13 @@
         <v>17832</v>
       </c>
       <c r="C342" s="33" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="D342" s="33" t="s">
         <v>40</v>
       </c>
       <c r="E342" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F342" s="4" t="str">
         <f t="shared" si="8"/>
@@ -46089,7 +46072,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="343" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A343" s="31">
         <v>2018</v>
       </c>
@@ -46103,7 +46086,7 @@
         <v>29</v>
       </c>
       <c r="E343" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F343" s="4">
         <f t="shared" si="8"/>
@@ -46215,7 +46198,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="344" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A344" s="31">
         <v>2018</v>
       </c>
@@ -46229,7 +46212,7 @@
         <v>36</v>
       </c>
       <c r="E344" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F344" s="4">
         <f t="shared" si="8"/>
@@ -46341,7 +46324,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="345" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A345" s="31">
         <v>2018</v>
       </c>
@@ -46355,7 +46338,7 @@
         <v>36</v>
       </c>
       <c r="E345" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F345" s="4">
         <f t="shared" si="8"/>
@@ -46467,7 +46450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A346" s="31">
         <v>2018</v>
       </c>
@@ -46481,7 +46464,7 @@
         <v>70</v>
       </c>
       <c r="E346" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F346" s="4" t="str">
         <f t="shared" si="8"/>
@@ -46593,7 +46576,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="347" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A347" s="31">
         <v>2018</v>
       </c>
@@ -46607,7 +46590,7 @@
         <v>111</v>
       </c>
       <c r="E347" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F347" s="4">
         <f t="shared" si="8"/>
@@ -46719,7 +46702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="348" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A348" s="31">
         <v>2018</v>
       </c>
@@ -46733,7 +46716,7 @@
         <v>90</v>
       </c>
       <c r="E348" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F348" s="4" t="str">
         <f t="shared" si="8"/>
@@ -46845,7 +46828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="349" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A349" s="31">
         <v>2018</v>
       </c>
@@ -46859,7 +46842,7 @@
         <v>31</v>
       </c>
       <c r="E349" s="33" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F349" s="4" t="str">
         <f t="shared" si="8"/>
@@ -46971,7 +46954,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="350" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A350" s="31">
         <v>2018</v>
       </c>
@@ -46985,7 +46968,7 @@
         <v>46</v>
       </c>
       <c r="E350" s="33" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="F350" s="4" t="str">
         <f t="shared" si="8"/>
@@ -47097,7 +47080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="351" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A351" s="31">
         <v>2018</v>
       </c>
@@ -47111,7 +47094,7 @@
         <v>93</v>
       </c>
       <c r="E351" s="33" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F351" s="4" t="str">
         <f t="shared" si="8"/>
@@ -47223,7 +47206,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="352" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A352" s="31">
         <v>2018</v>
       </c>
@@ -47237,7 +47220,7 @@
         <v>29</v>
       </c>
       <c r="E352" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F352" s="4">
         <f t="shared" si="8"/>
@@ -47349,7 +47332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="353" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A353" s="31">
         <v>2018</v>
       </c>
@@ -47363,7 +47346,7 @@
         <v>93</v>
       </c>
       <c r="E353" s="33" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="F353" s="4" t="str">
         <f t="shared" si="8"/>
@@ -47475,7 +47458,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="354" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A354" s="31">
         <v>2018</v>
       </c>
@@ -47489,7 +47472,7 @@
         <v>93</v>
       </c>
       <c r="E354" s="33" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="F354" s="4" t="str">
         <f t="shared" si="8"/>
@@ -47601,7 +47584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A355" s="31">
         <v>2018</v>
       </c>
@@ -47615,7 +47598,7 @@
         <v>111</v>
       </c>
       <c r="E355" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F355" s="4" t="str">
         <f t="shared" si="8"/>
@@ -47727,7 +47710,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="356" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A356" s="31">
         <v>2018</v>
       </c>
@@ -47741,7 +47724,7 @@
         <v>31</v>
       </c>
       <c r="E356" s="33" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="F356" s="4" t="str">
         <f t="shared" si="8"/>
@@ -47853,7 +47836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="357" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A357" s="31">
         <v>2018</v>
       </c>
@@ -47867,7 +47850,7 @@
         <v>40</v>
       </c>
       <c r="E357" s="33" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="F357" s="4" t="str">
         <f t="shared" si="8"/>
@@ -47979,7 +47962,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="358" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A358" s="31">
         <v>2018</v>
       </c>
@@ -47993,7 +47976,7 @@
         <v>142</v>
       </c>
       <c r="E358" s="33" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="F358" s="4" t="str">
         <f t="shared" si="8"/>
@@ -48105,7 +48088,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="359" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A359" s="31">
         <v>2018</v>
       </c>
@@ -48119,7 +48102,7 @@
         <v>248</v>
       </c>
       <c r="E359" s="33" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="F359" s="4" t="str">
         <f t="shared" si="8"/>
@@ -48231,7 +48214,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="360" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A360" s="31">
         <v>2018</v>
       </c>
@@ -48245,7 +48228,7 @@
         <v>371</v>
       </c>
       <c r="E360" s="33" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="F360" s="4" t="str">
         <f t="shared" si="8"/>
@@ -48357,7 +48340,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="361" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A361" s="31">
         <v>2018</v>
       </c>
@@ -48371,7 +48354,7 @@
         <v>25</v>
       </c>
       <c r="E361" s="33" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="F361" s="4" t="str">
         <f t="shared" si="8"/>
@@ -48483,7 +48466,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="362" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A362" s="31">
         <v>2018</v>
       </c>
@@ -48497,7 +48480,7 @@
         <v>36</v>
       </c>
       <c r="E362" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F362" s="4">
         <f t="shared" si="8"/>
@@ -48609,7 +48592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="363" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A363" s="31">
         <v>2018</v>
       </c>
@@ -48623,7 +48606,7 @@
         <v>96</v>
       </c>
       <c r="E363" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F363" s="4" t="str">
         <f t="shared" si="8"/>
@@ -48735,7 +48718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="364" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A364" s="31">
         <v>2018</v>
       </c>
@@ -48743,13 +48726,13 @@
         <v>19157</v>
       </c>
       <c r="C364" s="33" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="D364" s="33" t="s">
         <v>38</v>
       </c>
       <c r="E364" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F364" s="4">
         <f t="shared" si="8"/>
@@ -48861,7 +48844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A365" s="31">
         <v>2018</v>
       </c>
@@ -48869,13 +48852,13 @@
         <v>19157</v>
       </c>
       <c r="C365" s="33" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="D365" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E365" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F365" s="4">
         <f t="shared" si="8"/>
@@ -48987,7 +48970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="366" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A366" s="31">
         <v>2018</v>
       </c>
@@ -49001,7 +48984,7 @@
         <v>90</v>
       </c>
       <c r="E366" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F366" s="4" t="str">
         <f t="shared" si="8"/>
@@ -49113,7 +49096,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="367" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A367" s="31">
         <v>2018</v>
       </c>
@@ -49127,7 +49110,7 @@
         <v>46</v>
       </c>
       <c r="E367" s="33" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="F367" s="4" t="str">
         <f t="shared" si="8"/>
@@ -49239,7 +49222,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="368" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A368" s="31">
         <v>2018</v>
       </c>
@@ -49247,13 +49230,13 @@
         <v>19327</v>
       </c>
       <c r="C368" s="33" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="D368" s="33" t="s">
         <v>54</v>
       </c>
       <c r="E368" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F368" s="4">
         <f t="shared" si="8"/>
@@ -49365,7 +49348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A369" s="31">
         <v>2018</v>
       </c>
@@ -49379,7 +49362,7 @@
         <v>116</v>
       </c>
       <c r="E369" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F369" s="4">
         <f t="shared" si="8"/>
@@ -49491,7 +49474,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A370" s="31">
         <v>2018</v>
       </c>
@@ -49505,7 +49488,7 @@
         <v>142</v>
       </c>
       <c r="E370" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F370" s="4">
         <f t="shared" si="8"/>
@@ -49617,7 +49600,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="371" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A371" s="31">
         <v>2018</v>
       </c>
@@ -49631,7 +49614,7 @@
         <v>54</v>
       </c>
       <c r="E371" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F371" s="4">
         <f t="shared" si="8"/>
@@ -49743,7 +49726,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="372" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A372" s="31">
         <v>2018</v>
       </c>
@@ -49757,7 +49740,7 @@
         <v>104</v>
       </c>
       <c r="E372" s="33" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F372" s="4">
         <f t="shared" si="8"/>
@@ -49869,7 +49852,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="373" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A373" s="31">
         <v>2018</v>
       </c>
@@ -49883,7 +49866,7 @@
         <v>229</v>
       </c>
       <c r="E373" s="33" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="F373" s="4">
         <f t="shared" si="8"/>
@@ -49995,7 +49978,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="374" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A374" s="31">
         <v>2018</v>
       </c>
@@ -50009,7 +49992,7 @@
         <v>77</v>
       </c>
       <c r="E374" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F374" s="4">
         <f t="shared" si="8"/>
@@ -50121,7 +50104,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="375" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A375" s="31">
         <v>2018</v>
       </c>
@@ -50135,7 +50118,7 @@
         <v>46</v>
       </c>
       <c r="E375" s="33" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F375" s="4" t="str">
         <f t="shared" si="8"/>
@@ -50247,7 +50230,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="376" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A376" s="31">
         <v>2018</v>
       </c>
@@ -50261,7 +50244,7 @@
         <v>64</v>
       </c>
       <c r="E376" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F376" s="4">
         <f t="shared" si="8"/>
@@ -50373,7 +50356,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="377" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A377" s="31">
         <v>2018</v>
       </c>
@@ -50387,7 +50370,7 @@
         <v>77</v>
       </c>
       <c r="E377" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F377" s="4">
         <f t="shared" si="8"/>
@@ -50499,7 +50482,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="378" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A378" s="31">
         <v>2018</v>
       </c>
@@ -50507,13 +50490,13 @@
         <v>19798</v>
       </c>
       <c r="C378" s="33" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="D378" s="33" t="s">
         <v>42</v>
       </c>
       <c r="E378" s="33" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F378" s="4" t="str">
         <f t="shared" si="8"/>
@@ -50625,7 +50608,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="379" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A379" s="31">
         <v>2018</v>
       </c>
@@ -50639,7 +50622,7 @@
         <v>29</v>
       </c>
       <c r="E379" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F379" s="4">
         <f t="shared" si="8"/>
@@ -50751,7 +50734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A380" s="31">
         <v>2018</v>
       </c>
@@ -50765,7 +50748,7 @@
         <v>72</v>
       </c>
       <c r="E380" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F380" s="4" t="str">
         <f t="shared" si="8"/>
@@ -50877,7 +50860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="381" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A381" s="31">
         <v>2018</v>
       </c>
@@ -50891,7 +50874,7 @@
         <v>79</v>
       </c>
       <c r="E381" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F381" s="4">
         <f t="shared" si="8"/>
@@ -51003,7 +50986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A382" s="31">
         <v>2018</v>
       </c>
@@ -51017,7 +51000,7 @@
         <v>25</v>
       </c>
       <c r="E382" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F382" s="4">
         <f t="shared" si="8"/>
@@ -51129,7 +51112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A383" s="31">
         <v>2018</v>
       </c>
@@ -51137,13 +51120,13 @@
         <v>19896</v>
       </c>
       <c r="C383" s="33" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="D383" s="33" t="s">
         <v>64</v>
       </c>
       <c r="E383" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F383" s="4" t="str">
         <f t="shared" si="8"/>
@@ -51255,7 +51238,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="384" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A384" s="31">
         <v>2018</v>
       </c>
@@ -51269,7 +51252,7 @@
         <v>36</v>
       </c>
       <c r="E384" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F384" s="4">
         <f t="shared" si="8"/>
@@ -51381,7 +51364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A385" s="31">
         <v>2018</v>
       </c>
@@ -51395,7 +51378,7 @@
         <v>96</v>
       </c>
       <c r="E385" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F385" s="4">
         <f t="shared" si="8"/>
@@ -51507,7 +51490,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="386" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A386" s="31">
         <v>2018</v>
       </c>
@@ -51521,7 +51504,7 @@
         <v>70</v>
       </c>
       <c r="E386" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F386" s="4">
         <f t="shared" si="8"/>
@@ -51633,7 +51616,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="387" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A387" s="31">
         <v>2018</v>
       </c>
@@ -51647,7 +51630,7 @@
         <v>79</v>
       </c>
       <c r="E387" s="33" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F387" s="4" t="str">
         <f t="shared" si="8"/>
@@ -51759,7 +51742,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="388" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A388" s="31">
         <v>2018</v>
       </c>
@@ -51773,7 +51756,7 @@
         <v>36</v>
       </c>
       <c r="E388" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F388" s="4">
         <f t="shared" si="8"/>
@@ -51885,7 +51868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="389" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A389" s="31">
         <v>2018</v>
       </c>
@@ -51899,7 +51882,7 @@
         <v>89</v>
       </c>
       <c r="E389" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F389" s="4">
         <f t="shared" ref="F389:H430" si="10">IFERROR(SUM(AD389,AI389)*10^3/T389,"")</f>
@@ -52011,7 +51994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="390" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A390" s="31">
         <v>2018</v>
       </c>
@@ -52025,7 +52008,7 @@
         <v>64</v>
       </c>
       <c r="E390" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F390" s="4">
         <f t="shared" si="10"/>
@@ -52137,7 +52120,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="391" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A391" s="31">
         <v>2018</v>
       </c>
@@ -52151,7 +52134,7 @@
         <v>54</v>
       </c>
       <c r="E391" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F391" s="4" t="str">
         <f t="shared" si="10"/>
@@ -52263,7 +52246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A392" s="31">
         <v>2018</v>
       </c>
@@ -52277,7 +52260,7 @@
         <v>70</v>
       </c>
       <c r="E392" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F392" s="4" t="str">
         <f t="shared" si="10"/>
@@ -52389,7 +52372,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="393" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A393" s="31">
         <v>2018</v>
       </c>
@@ -52403,7 +52386,7 @@
         <v>54</v>
       </c>
       <c r="E393" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F393" s="4">
         <f t="shared" si="10"/>
@@ -52515,7 +52498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="394" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A394" s="31">
         <v>2018</v>
       </c>
@@ -52523,13 +52506,13 @@
         <v>20477</v>
       </c>
       <c r="C394" s="33" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="D394" s="33" t="s">
         <v>96</v>
       </c>
       <c r="E394" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F394" s="4">
         <f t="shared" si="10"/>
@@ -52641,7 +52624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="395" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A395" s="31">
         <v>2018</v>
       </c>
@@ -52655,7 +52638,7 @@
         <v>44</v>
       </c>
       <c r="E395" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F395" s="4">
         <f t="shared" si="10"/>
@@ -52767,7 +52750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="396" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A396" s="31">
         <v>2018</v>
       </c>
@@ -52775,13 +52758,13 @@
         <v>20603</v>
       </c>
       <c r="C396" s="33" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="D396" s="33" t="s">
         <v>68</v>
       </c>
       <c r="E396" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F396" s="4">
         <f t="shared" si="10"/>
@@ -52893,7 +52876,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="397" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A397" s="31">
         <v>2018</v>
       </c>
@@ -52907,7 +52890,7 @@
         <v>36</v>
       </c>
       <c r="E397" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F397" s="4">
         <f t="shared" si="10"/>
@@ -53019,7 +53002,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="398" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A398" s="31">
         <v>2018</v>
       </c>
@@ -53033,7 +53016,7 @@
         <v>36</v>
       </c>
       <c r="E398" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F398" s="4">
         <f t="shared" si="10"/>
@@ -53145,7 +53128,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="399" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A399" s="31">
         <v>2018</v>
       </c>
@@ -53159,7 +53142,7 @@
         <v>64</v>
       </c>
       <c r="E399" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F399" s="4">
         <f t="shared" si="10"/>
@@ -53271,7 +53254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="400" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A400" s="31">
         <v>2018</v>
       </c>
@@ -53285,7 +53268,7 @@
         <v>31</v>
       </c>
       <c r="E400" s="33" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F400" s="4">
         <f t="shared" si="10"/>
@@ -53397,7 +53380,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="401" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A401" s="31">
         <v>2018</v>
       </c>
@@ -53411,7 +53394,7 @@
         <v>29</v>
       </c>
       <c r="E401" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F401" s="4" t="str">
         <f t="shared" si="10"/>
@@ -53523,7 +53506,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="402" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A402" s="31">
         <v>2018</v>
       </c>
@@ -53537,7 +53520,7 @@
         <v>29</v>
       </c>
       <c r="E402" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F402" s="4" t="str">
         <f t="shared" si="10"/>
@@ -53649,7 +53632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A403" s="31">
         <v>2018</v>
       </c>
@@ -53657,13 +53640,13 @@
         <v>20858</v>
       </c>
       <c r="C403" s="33" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="D403" s="33" t="s">
         <v>29</v>
       </c>
       <c r="E403" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F403" s="4" t="str">
         <f t="shared" si="10"/>
@@ -53775,7 +53758,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="404" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A404" s="31">
         <v>2018</v>
       </c>
@@ -53789,7 +53772,7 @@
         <v>29</v>
       </c>
       <c r="E404" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F404" s="4">
         <f t="shared" si="10"/>
@@ -53901,7 +53884,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="405" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A405" s="31">
         <v>2018</v>
       </c>
@@ -53915,7 +53898,7 @@
         <v>48</v>
       </c>
       <c r="E405" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F405" s="4" t="str">
         <f t="shared" si="10"/>
@@ -54027,7 +54010,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="406" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A406" s="31">
         <v>2018</v>
       </c>
@@ -54041,7 +54024,7 @@
         <v>62</v>
       </c>
       <c r="E406" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F406" s="4">
         <f t="shared" si="10"/>
@@ -54153,7 +54136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="407" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A407" s="31">
         <v>2018</v>
       </c>
@@ -54167,7 +54150,7 @@
         <v>36</v>
       </c>
       <c r="E407" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F407" s="4">
         <f t="shared" si="10"/>
@@ -54279,7 +54262,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="408" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A408" s="31">
         <v>2018</v>
       </c>
@@ -54293,7 +54276,7 @@
         <v>25</v>
       </c>
       <c r="E408" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F408" s="4">
         <f t="shared" si="10"/>
@@ -54405,7 +54388,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="409" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A409" s="31">
         <v>2018</v>
       </c>
@@ -54413,13 +54396,13 @@
         <v>21554</v>
       </c>
       <c r="C409" s="33" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="D409" s="33" t="s">
         <v>93</v>
       </c>
       <c r="E409" s="33" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F409" s="4" t="str">
         <f t="shared" si="10"/>
@@ -54531,7 +54514,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="410" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A410" s="31">
         <v>2018</v>
       </c>
@@ -54545,7 +54528,7 @@
         <v>79</v>
       </c>
       <c r="E410" s="33" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="F410" s="4">
         <f t="shared" si="10"/>
@@ -54657,7 +54640,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="411" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A411" s="31">
         <v>2018</v>
       </c>
@@ -54671,7 +54654,7 @@
         <v>72</v>
       </c>
       <c r="E411" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F411" s="4" t="str">
         <f t="shared" si="10"/>
@@ -54783,7 +54766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="412" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A412" s="31">
         <v>2018</v>
       </c>
@@ -54797,7 +54780,7 @@
         <v>72</v>
       </c>
       <c r="E412" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F412" s="4" t="str">
         <f t="shared" si="10"/>
@@ -54909,7 +54892,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="413" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A413" s="31">
         <v>2018</v>
       </c>
@@ -54923,7 +54906,7 @@
         <v>46</v>
       </c>
       <c r="E413" s="33" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F413" s="4" t="str">
         <f t="shared" si="10"/>
@@ -55035,7 +55018,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="414" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A414" s="31">
         <v>2018</v>
       </c>
@@ -55049,7 +55032,7 @@
         <v>77</v>
       </c>
       <c r="E414" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F414" s="4">
         <f t="shared" si="10"/>
@@ -55161,7 +55144,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="415" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A415" s="31">
         <v>2018</v>
       </c>
@@ -55175,7 +55158,7 @@
         <v>68</v>
       </c>
       <c r="E415" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F415" s="4" t="str">
         <f t="shared" si="10"/>
@@ -55287,7 +55270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="416" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A416" s="31">
         <v>2018</v>
       </c>
@@ -55301,7 +55284,7 @@
         <v>40</v>
       </c>
       <c r="E416" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F416" s="4" t="str">
         <f t="shared" si="10"/>
@@ -55413,7 +55396,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="417" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A417" s="31">
         <v>2018</v>
       </c>
@@ -55427,7 +55410,7 @@
         <v>36</v>
       </c>
       <c r="E417" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F417" s="4">
         <f t="shared" si="10"/>
@@ -55539,7 +55522,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="418" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A418" s="31">
         <v>2018</v>
       </c>
@@ -55553,7 +55536,7 @@
         <v>36</v>
       </c>
       <c r="E418" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F418" s="4">
         <f t="shared" si="10"/>
@@ -55665,7 +55648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="419" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A419" s="31">
         <v>2018</v>
       </c>
@@ -55679,7 +55662,7 @@
         <v>54</v>
       </c>
       <c r="E419" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F419" s="4" t="str">
         <f t="shared" si="10"/>
@@ -55791,7 +55774,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="420" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A420" s="31">
         <v>2018</v>
       </c>
@@ -55805,7 +55788,7 @@
         <v>291</v>
       </c>
       <c r="E420" s="33" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F420" s="4" t="str">
         <f t="shared" si="10"/>
@@ -55917,7 +55900,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="421" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A421" s="31">
         <v>2018</v>
       </c>
@@ -55931,7 +55914,7 @@
         <v>27</v>
       </c>
       <c r="E421" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F421" s="4">
         <f t="shared" si="10"/>
@@ -56043,7 +56026,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="422" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A422" s="31">
         <v>2018</v>
       </c>
@@ -56057,7 +56040,7 @@
         <v>68</v>
       </c>
       <c r="E422" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F422" s="4">
         <f t="shared" si="10"/>
@@ -56169,7 +56152,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="423" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A423" s="31">
         <v>2018</v>
       </c>
@@ -56183,7 +56166,7 @@
         <v>68</v>
       </c>
       <c r="E423" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F423" s="4">
         <f t="shared" si="10"/>
@@ -56295,7 +56278,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="424" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A424" s="31">
         <v>2018</v>
       </c>
@@ -56309,7 +56292,7 @@
         <v>106</v>
       </c>
       <c r="E424" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F424" s="4">
         <f t="shared" si="10"/>
@@ -56421,7 +56404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="425" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A425" s="31">
         <v>2018</v>
       </c>
@@ -56435,7 +56418,7 @@
         <v>40</v>
       </c>
       <c r="E425" s="33" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F425" s="4" t="str">
         <f t="shared" si="10"/>
@@ -56547,7 +56530,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="426" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A426" s="31">
         <v>2018</v>
       </c>
@@ -56561,7 +56544,7 @@
         <v>25</v>
       </c>
       <c r="E426" s="33" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F426" s="4">
         <f t="shared" si="10"/>
@@ -56673,7 +56656,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="427" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A427" s="31">
         <v>2018</v>
       </c>
@@ -56687,7 +56670,7 @@
         <v>54</v>
       </c>
       <c r="E427" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F427" s="4">
         <f t="shared" si="10"/>
@@ -56799,7 +56782,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="428" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A428" s="31">
         <v>2018</v>
       </c>
@@ -56813,7 +56796,7 @@
         <v>42</v>
       </c>
       <c r="E428" s="33" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F428" s="4" t="str">
         <f t="shared" si="10"/>
@@ -56925,7 +56908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A429" s="31">
         <v>2018</v>
       </c>
@@ -56939,7 +56922,7 @@
         <v>54</v>
       </c>
       <c r="E429" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F429" s="4" t="str">
         <f t="shared" si="10"/>
@@ -57051,7 +57034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="430" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A430" s="31">
         <v>2018</v>
       </c>
@@ -57059,13 +57042,13 @@
         <v>58127</v>
       </c>
       <c r="C430" s="33" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="D430" s="33" t="s">
         <v>111</v>
       </c>
       <c r="E430" s="33" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="F430" s="4" t="str">
         <f t="shared" si="10"/>
@@ -57177,7 +57160,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="431" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A431" s="31">
         <v>2018</v>
       </c>
@@ -57191,7 +57174,7 @@
         <v>90</v>
       </c>
       <c r="E431" s="33" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F431" s="4">
         <f t="shared" ref="F431:H432" si="11">IFERROR(SUM(AD431,AI431)*10^3/T431,"")</f>
@@ -57303,7 +57286,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="432" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A432" s="31">
         <v>2018</v>
       </c>
@@ -57311,13 +57294,13 @@
         <v>60631</v>
       </c>
       <c r="C432" s="33" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="D432" s="33" t="s">
         <v>116</v>
       </c>
       <c r="E432" s="33" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F432" s="36">
         <f t="shared" si="11"/>
@@ -57430,7 +57413,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AN430"/>
+  <autoFilter ref="A3:AN430" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="J1:AC1"/>
@@ -57450,51 +57433,51 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.86328125" customWidth="1"/>
-    <col min="2" max="2" width="26.73046875" customWidth="1"/>
-    <col min="3" max="3" width="21.1328125" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="9"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="9"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="9"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>437</v>
       </c>
@@ -57507,7 +57490,7 @@
         <v>0.27639423854992745</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>438</v>
       </c>
@@ -57520,7 +57503,7 @@
         <v>0.22725360090629559</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>439</v>
       </c>
@@ -57533,22 +57516,22 @@
         <v>0.49636510762259262</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>437</v>
       </c>
@@ -57561,7 +57544,7 @@
         <v>0.27639423854992745</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>444</v>
       </c>
@@ -57581,127 +57564,86 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.3984375" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
+        <v>555</v>
+      </c>
       <c r="B1" s="14" t="s">
-        <v>470</v>
+        <v>556</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>436</v>
       </c>
       <c r="B2" s="11">
-        <f>Calculations!B17*About!$A$34*About!$A$37</f>
-        <v>906.86645626780012</v>
+        <f>Calculations!B17*About!$A$34</f>
+        <v>23383.101272803659</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B3" s="11">
+        <f>Calculations!B17*About!$A$34</f>
+        <v>23383.101272803659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>462</v>
       </c>
-      <c r="B3" s="11">
-        <f>Calculations!B17*About!$A$34*About!$A$37</f>
-        <v>906.86645626780012</v>
+      <c r="B4" s="11">
+        <f>Calculations!B16*About!$A$34</f>
+        <v>37946.092485549132</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>463</v>
       </c>
-      <c r="B4" s="11">
-        <f>Calculations!B16*About!$A$34*About!$A$37</f>
-        <v>1471.6627200175531</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>464</v>
-      </c>
       <c r="B5">
         <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>465</v>
-      </c>
-      <c r="B6" s="11">
-        <f>B$3</f>
-        <v>906.86645626780012</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>466</v>
-      </c>
-      <c r="B7" s="11">
-        <f t="shared" ref="B7:B10" si="0">B$3</f>
-        <v>906.86645626780012</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>467</v>
-      </c>
-      <c r="B8" s="11">
-        <f t="shared" si="0"/>
-        <v>906.86645626780012</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>468</v>
-      </c>
-      <c r="B9" s="11">
-        <f t="shared" si="0"/>
-        <v>906.86645626780012</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>469</v>
-      </c>
-      <c r="B10" s="11">
-        <f t="shared" si="0"/>
-        <v>906.86645626780012</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.265625" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>471</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="65" t="s">
+        <v>557</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>436</v>
       </c>
@@ -57709,69 +57651,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B3" s="13">
+        <f>Calculations!C17</f>
+        <v>0.72361870852888821</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>462</v>
       </c>
-      <c r="B3" s="13">
-        <f>Calculations!C17*About!$A$37</f>
-        <v>2.8064093220000533E-2</v>
+      <c r="B4" s="13">
+        <f>Calculations!C16</f>
+        <v>0.27639423854992745</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>463</v>
       </c>
-      <c r="B4" s="13">
-        <f>Calculations!C16*About!$A$37</f>
-        <v>1.0719393493716678E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>464</v>
-      </c>
       <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>465</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>466</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>467</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>468</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>469</v>
-      </c>
-      <c r="B10">
         <v>0</v>
       </c>
     </row>
